--- a/knowledge/RehabMind_ClinicalExtension_v1.1.xlsx
+++ b/knowledge/RehabMind_ClinicalExtension_v1.1.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DimensionGuide" sheetId="1" r:id="Re47a915d2ccb4adc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClinicalPurpose" sheetId="2" r:id="Rd640a380f22f4d0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FindingFeature" sheetId="3" r:id="R2afc1a43b07f445a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="InterventionReference" sheetId="4" r:id="R8726ceef80d74905"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ConsultationGuide" sheetId="5" r:id="R91da05b42a9e4353"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LocationGuide" sheetId="6" r:id="R9aada19e51ed46f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DimensionGuide" sheetId="1" r:id="R8f3051e13f4947cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClinicalPurpose" sheetId="2" r:id="R9bec21b349904a8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FindingFeature" sheetId="3" r:id="R21c34ed7de9f4b58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="InterventionReference" sheetId="4" r:id="R0d0183ed48d945eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ConsultationGuide" sheetId="5" r:id="R6843365527454f9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LocationGuide" sheetId="6" r:id="Raaa58e1ef2624dcc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19061,12 +19061,15 @@
         <x:v>第2阶段部位问诊由已有临床项目和用户确认的产品边界整理，待临床审核；肿胀包块提示参考 https://www.nhs.uk/conditions/bakers-cyst/ 。不录入回答，不自动触发评估或处理。</x:v>
       </x:c>
       <x:c r="O8" s="9" t="str">
-        <x:v>部位问诊编辑样例；仅展示，不解析回答。</x:v>
+        <x:v>部位问诊编辑样例；仅展示，不解析回答。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P8" s="9" t="str">
         <x:v>LOC-KNEE-CALF-POST</x:v>
       </x:c>
-      <x:c r="Q8" s="9"/>
+      <x:c r="Q8" s="9" t="str">
+        <x:v>QG-KNEE-POST-1</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="112" customHeight="1">
       <x:c r="A9" s="9" t="str">
@@ -19110,13 +19113,14 @@
         <x:v>第2阶段部位问诊由已有临床项目和用户确认的产品边界整理，待临床审核；肿胀包块提示参考 https://www.nhs.uk/conditions/bakers-cyst/ 。不录入回答，不自动触发评估或处理。</x:v>
       </x:c>
       <x:c r="O9" s="9" t="str">
-        <x:v>部位问诊编辑样例；仅展示，不解析回答。</x:v>
+        <x:v>部位问诊编辑样例；仅展示，不解析回答。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P9" s="9" t="str">
         <x:v>LOC-KNEE-CALF-POST</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str">
-        <x:v>QG-PROVOKE</x:v>
+        <x:v>QG-PROVOKE|QG-KNEE-POST-2</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="112" customHeight="1">
@@ -19188,7 +19192,7 @@
         <x:v>肿胀或包块的位置、变化经过，以及皮肤触感和感觉变化。</x:v>
       </x:c>
       <x:c r="G11" s="9" t="str">
-        <x:v>提示关注腘窝及近端小腿局部组织；感觉变化可补充神经筛查，突然加重的肿痛或发热需进一步评估。</x:v>
+        <x:v>结合膝后局部组织与感觉、力量检查；新发单侧明显肿胀、发热或变色，应先安排医学评估，不先做反复负重或深压测试。</x:v>
       </x:c>
       <x:c r="H11" s="9" t="str">
         <x:v>LOCATION</x:v>
@@ -19210,12 +19214,15 @@
         <x:v>第2阶段部位问诊由已有临床项目和用户确认的产品边界整理，待临床审核；肿胀包块提示参考 https://www.nhs.uk/conditions/bakers-cyst/ 。不录入回答，不自动触发评估或处理。</x:v>
       </x:c>
       <x:c r="O11" s="9" t="str">
-        <x:v>部位问诊编辑样例；仅展示，不解析回答。</x:v>
+        <x:v>部位问诊编辑样例；仅展示，不解析回答。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P11" s="9" t="str">
         <x:v>LOC-KNEE-CALF-POST</x:v>
       </x:c>
-      <x:c r="Q11" s="9"/>
+      <x:c r="Q11" s="9" t="str">
+        <x:v>QG-KNEE-POST-3</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="80" customHeight="1">
       <x:c r="A12" s="9" t="str">
@@ -19225,7 +19232,7 @@
         <x:v>骨缘还是后侧软组织</x:v>
       </x:c>
       <x:c r="C12" s="9" t="str">
-        <x:v>不适在胫骨内侧边缘，还是骨缘后方的软组织？</x:v>
+        <x:v>小腿内侧最不舒服的位置在哪里？靠近硬的骨边，还是更后面的软组织？</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
         <x:v>是一个点还是沿着一段？偏上段、中段还是下段？</x:v>
@@ -19259,12 +19266,15 @@
         <x:v>本批部位问诊为编辑稿，待临床审核；基础检查来自主库 Lower Leg Remaining L3 Review v2.6、Core Assessment Protocol Refinement v3.2。参考 https://www.orthoinfo.org/diseases--conditions/shin-splints/ 及 https://www.orthoinfo.org/diseases--conditions/posterior-tibial-tendon-dysfunction/ ，只支持问诊和评估背景，不支持由位置诊断或自动处理。</x:v>
       </x:c>
       <x:c r="O12" s="9" t="str">
-        <x:v>问诊展示稿，无答案录入或自动选择。</x:v>
+        <x:v>问诊展示稿，无答案录入或自动选择。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P12" s="9" t="str">
         <x:v>LOC-LL-MEDIAL</x:v>
       </x:c>
-      <x:c r="Q12" s="9"/>
+      <x:c r="Q12" s="9" t="str">
+        <x:v>QG-LM-LOCATION-REGION|QG-LM-ACTIVITY-REGION|QG-LM-CHANGE-REGION|QG-LM-ASSOCIATED-REGION|QG-LPM-LOCATION-REGION|QG-LPM-ACTIVITY-REGION|QG-LPM-CHANGE-REGION|QG-LPM-ASSOCIATED-REGION</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="80" customHeight="1">
       <x:c r="A13" s="9" t="str">
@@ -19457,12 +19467,15 @@
         <x:v>本批部位问诊为编辑稿，待临床审核；基础检查来自主库 Lower Leg Remaining L3 Review v2.6、Core Assessment Protocol Refinement v3.2。参考 https://www.orthoinfo.org/diseases--conditions/shin-splints/ 及 https://www.orthoinfo.org/diseases--conditions/posterior-tibial-tendon-dysfunction/ ，只支持问诊和评估背景，不支持由位置诊断或自动处理。</x:v>
       </x:c>
       <x:c r="O16" s="9" t="str">
-        <x:v>问诊展示稿，无答案录入或自动选择。</x:v>
+        <x:v>问诊展示稿，无答案录入或自动选择。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P16" s="9" t="str">
         <x:v>LOC-LL-POSTMEDIAL</x:v>
       </x:c>
-      <x:c r="Q16" s="9"/>
+      <x:c r="Q16" s="9" t="str">
+        <x:v>QG-LM-LOCATION-REGION|QG-LM-ACTIVITY-REGION|QG-LM-CHANGE-REGION|QG-LM-ASSOCIATED-REGION|QG-LPM-LOCATION-REGION|QG-LPM-ACTIVITY-REGION|QG-LPM-CHANGE-REGION|QG-LPM-ASSOCIATED-REGION</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="80" customHeight="1">
       <x:c r="A17" s="9" t="str">
@@ -19584,7 +19597,7 @@
         <x:v>感觉分布、肿胀范围与变化经过。</x:v>
       </x:c>
       <x:c r="G19" s="9" t="str">
-        <x:v>可补充局部组织和神经筛查；突然出现的明显肿胀需进一步评估。</x:v>
+        <x:v>感觉异常需结合分布补充神经筛查；新发单侧明显肿胀、发热或变色，应先安排医学评估，不以肌肉紧张解释。</x:v>
       </x:c>
       <x:c r="H19" s="9" t="str">
         <x:v>LOCATION</x:v>
@@ -19606,7 +19619,8 @@
         <x:v>本批部位问诊为编辑稿，待临床审核；基础检查来自主库 Lower Leg Remaining L3 Review v2.6、Core Assessment Protocol Refinement v3.2。参考 https://www.orthoinfo.org/diseases--conditions/shin-splints/ 及 https://www.orthoinfo.org/diseases--conditions/posterior-tibial-tendon-dysfunction/ ，只支持问诊和评估背景，不支持由位置诊断或自动处理。</x:v>
       </x:c>
       <x:c r="O19" s="9" t="str">
-        <x:v>问诊展示稿，无答案录入或自动选择。</x:v>
+        <x:v>问诊展示稿，无答案录入或自动选择。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P19" s="9" t="str">
         <x:v>LOC-LL-POSTMEDIAL</x:v>
@@ -19822,7 +19836,7 @@
         <x:v>胫骨前面的疼痛是集中在一个点，还是沿着一段？</x:v>
       </x:c>
       <x:c r="D24" s="9" t="str">
-        <x:v>骨面按压和旁边肌肉按压，哪里更不舒服？有没有局部肿胀？</x:v>
+        <x:v>能用一个手指指出最明显的位置吗？是在硬的骨面上还是旁边？有没有肿胀？无需患者自行反复按压。</x:v>
       </x:c>
       <x:c r="E24" s="9" t="str">
         <x:v>了解骨面与邻近肌腹的压痛分布。</x:v>
@@ -19853,7 +19867,8 @@
         <x:v>部位问诊及临床文案为待临床审核编辑稿。基础项目来自主库 Lower Leg Anterior/Tibial Review v2.5 与 Core Assessment Protocol Refinement v3.2；解剖参考 NCBI Bookshelf NBK539725，活动和力量方法参考 AAOS Foot and Ankle Conditioning Program 2025。具体松解和募集方法引用已索引的授权线下记录。问诊不录入答案、不触发项目或方法。</x:v>
       </x:c>
       <x:c r="O24" s="9" t="str">
-        <x:v>仅展示问诊思路，不解析回答或自动安排评估。</x:v>
+        <x:v>仅展示问诊思路，不解析回答或自动安排评估。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P24" s="9" t="str">
         <x:v>LOC-LL-ANTERIOR-BONE</x:v>
@@ -20249,10 +20264,11 @@
         <x:v>本批为待临床审核编辑稿。部位、检查项目及膝位比较沿用主库Lower Leg Remaining L3 Review v2.6、Ankle DF Protocol Alignment v3.3及Core Assessment Protocol Refinement v3.2。肌腹方法引用授权记录；伸膝/屈膝牵伸核对Royal Orthopaedic Hospital，坐位/站立提踵核对Torbay NHS。不迁移急性拉伤或跟腱病的完整方案，不添加剂量、治疗选择或问诊答案。</x:v>
       </x:c>
       <x:c r="O32" s="9" t="str">
-        <x:v>仅展示问诊思路，不解析回答或自动安排评估。</x:v>
+        <x:v>仅展示问诊思路，不解析回答或自动安排评估。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P32" s="9" t="str">
-        <x:v>LOC-LL-POSTUPPER</x:v>
+        <x:v>LOC-LL-POSTUPPER|LOC-LL-GASTROC-MEDIAL|LOC-LL-GASTROC-LATERAL</x:v>
       </x:c>
       <x:c r="Q32" s="9"/>
     </x:row>
@@ -20298,10 +20314,11 @@
         <x:v>本批为待临床审核编辑稿。部位、检查项目及膝位比较沿用主库Lower Leg Remaining L3 Review v2.6、Ankle DF Protocol Alignment v3.3及Core Assessment Protocol Refinement v3.2。肌腹方法引用授权记录；伸膝/屈膝牵伸核对Royal Orthopaedic Hospital，坐位/站立提踵核对Torbay NHS。不迁移急性拉伤或跟腱病的完整方案，不添加剂量、治疗选择或问诊答案。</x:v>
       </x:c>
       <x:c r="O33" s="9" t="str">
-        <x:v>仅展示问诊思路，不解析回答或自动安排评估。</x:v>
+        <x:v>仅展示问诊思路，不解析回答或自动安排评估。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P33" s="9" t="str">
-        <x:v>LOC-LL-POSTUPPER</x:v>
+        <x:v>LOC-LL-POSTUPPER|LOC-LL-GASTROC-MEDIAL|LOC-LL-GASTROC-LATERAL</x:v>
       </x:c>
       <x:c r="Q33" s="9" t="str">
         <x:v>QG-PROVOKE</x:v>
@@ -20349,10 +20366,11 @@
         <x:v>本批为待临床审核编辑稿。部位、检查项目及膝位比较沿用主库Lower Leg Remaining L3 Review v2.6、Ankle DF Protocol Alignment v3.3及Core Assessment Protocol Refinement v3.2。肌腹方法引用授权记录；伸膝/屈膝牵伸核对Royal Orthopaedic Hospital，坐位/站立提踵核对Torbay NHS。不迁移急性拉伤或跟腱病的完整方案，不添加剂量、治疗选择或问诊答案。</x:v>
       </x:c>
       <x:c r="O34" s="9" t="str">
-        <x:v>仅展示问诊思路，不解析回答或自动安排评估。</x:v>
+        <x:v>仅展示问诊思路，不解析回答或自动安排评估。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P34" s="9" t="str">
-        <x:v>LOC-LL-POSTUPPER</x:v>
+        <x:v>LOC-LL-POSTUPPER|LOC-LL-GASTROC-MEDIAL|LOC-LL-GASTROC-LATERAL</x:v>
       </x:c>
       <x:c r="Q34" s="9"/>
     </x:row>
@@ -20398,10 +20416,11 @@
         <x:v>本批为待临床审核编辑稿。部位、检查项目及膝位比较沿用主库Lower Leg Remaining L3 Review v2.6、Ankle DF Protocol Alignment v3.3及Core Assessment Protocol Refinement v3.2。肌腹方法引用授权记录；伸膝/屈膝牵伸核对Royal Orthopaedic Hospital，坐位/站立提踵核对Torbay NHS。不迁移急性拉伤或跟腱病的完整方案，不添加剂量、治疗选择或问诊答案。</x:v>
       </x:c>
       <x:c r="O35" s="9" t="str">
-        <x:v>仅展示问诊思路，不解析回答或自动安排评估。</x:v>
+        <x:v>仅展示问诊思路，不解析回答或自动安排评估。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P35" s="9" t="str">
-        <x:v>LOC-LL-POSTUPPER</x:v>
+        <x:v>LOC-LL-POSTUPPER|LOC-LL-GASTROC-MEDIAL|LOC-LL-GASTROC-LATERAL</x:v>
       </x:c>
       <x:c r="Q35" s="9"/>
     </x:row>
@@ -20704,7 +20723,8 @@
 https://www.kentcht.nhs.uk/leaflet/insertional-achilles-tendinopathy/</x:v>
       </x:c>
       <x:c r="O41" s="9" t="str">
-        <x:v>仅展示问诊思路，不解析回答或自动安排评估。</x:v>
+        <x:v>仅展示问诊思路，不解析回答或自动安排评估。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P41" s="9"/>
       <x:c r="Q41" s="9" t="str">
@@ -20865,7 +20885,8 @@
 https://www.kentcht.nhs.uk/leaflet/insertional-achilles-tendinopathy/</x:v>
       </x:c>
       <x:c r="O44" s="9" t="str">
-        <x:v>仅展示问诊思路，不解析回答或自动安排评估。</x:v>
+        <x:v>仅展示问诊思路，不解析回答或自动安排评估。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P44" s="9"/>
       <x:c r="Q44" s="9" t="str">
@@ -20892,7 +20913,7 @@
         <x:v>出现方式、形态及发力变化。</x:v>
       </x:c>
       <x:c r="G45" s="9" t="str">
-        <x:v>为跟腱完整性及损伤相关排查提供信息。</x:v>
+        <x:v>突然弹响或被踢感，伴明显蹬地无力时，先排查跟腱完整性并及时医学评估；暂缓强牵拉、反复提踵和跑跳测试。</x:v>
       </x:c>
       <x:c r="H45" s="9" t="str">
         <x:v>REGION</x:v>
@@ -20917,10 +20938,12 @@
 https://doi.org/10.2519/jospt.2024.0302
 https://doi.org/10.1136/bjsports-2024-109138
 https://myjointhealthhub.bnssg.nhs.uk/foot-ankle-pain/achilles-tendinopathy/
-https://www.kentcht.nhs.uk/leaflet/insertional-achilles-tendinopathy/</x:v>
+https://www.kentcht.nhs.uk/leaflet/insertional-achilles-tendinopathy/
+https://www.orthoinfo.org/diseases--conditions/achilles-tendon-rupture-tear/</x:v>
       </x:c>
       <x:c r="O45" s="9" t="str">
-        <x:v>仅展示问诊思路，不解析回答或自动安排评估。</x:v>
+        <x:v>仅展示问诊思路，不解析回答或自动安排评估。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P45" s="9"/>
       <x:c r="Q45" s="9"/>
@@ -21026,7 +21049,8 @@
 https://www.kentcht.nhs.uk/leaflet/insertional-achilles-tendinopathy/</x:v>
       </x:c>
       <x:c r="O47" s="9" t="str">
-        <x:v>仅展示问诊思路，不解析回答或自动安排评估。</x:v>
+        <x:v>仅展示问诊思路，不解析回答或自动安排评估。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P47" s="9"/>
       <x:c r="Q47" s="9" t="str">
@@ -21053,7 +21077,7 @@
         <x:v>出现经过、训练和鞋具背景及伴随表现。</x:v>
       </x:c>
       <x:c r="G48" s="9" t="str">
-        <x:v>为止点、邻近组织与损伤方向排查提供背景。</x:v>
+        <x:v>突然弹响或被踢感，伴明显蹬地无力时，先排查跟腱完整性并及时医学评估；暂缓强牵拉、反复提踵和跑跳测试。</x:v>
       </x:c>
       <x:c r="H48" s="9" t="str">
         <x:v>REGION</x:v>
@@ -21078,10 +21102,12 @@
 https://doi.org/10.2519/jospt.2024.0302
 https://doi.org/10.1136/bjsports-2024-109138
 https://myjointhealthhub.bnssg.nhs.uk/foot-ankle-pain/achilles-tendinopathy/
-https://www.kentcht.nhs.uk/leaflet/insertional-achilles-tendinopathy/</x:v>
+https://www.kentcht.nhs.uk/leaflet/insertional-achilles-tendinopathy/
+https://www.orthoinfo.org/diseases--conditions/achilles-tendon-rupture-tear/</x:v>
       </x:c>
       <x:c r="O48" s="9" t="str">
-        <x:v>仅展示问诊思路，不解析回答或自动安排评估。</x:v>
+        <x:v>仅展示问诊思路，不解析回答或自动安排评估。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P48" s="9"/>
       <x:c r="Q48" s="9"/>
@@ -21191,7 +21217,8 @@
 https://doi.org/10.1007/s00167-018-4971-x</x:v>
       </x:c>
       <x:c r="O50" s="9" t="str">
-        <x:v>仅展示问诊思路，不解析回答或自动安排评估。</x:v>
+        <x:v>仅展示问诊思路，不解析回答或自动安排评估。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P50" s="9"/>
       <x:c r="Q50" s="9" t="str">
@@ -21358,7 +21385,8 @@
 https://doi.org/10.1007/s00167-018-4971-x</x:v>
       </x:c>
       <x:c r="O53" s="9" t="str">
-        <x:v>仅展示问诊思路，不解析回答或自动安排评估。</x:v>
+        <x:v>仅展示问诊思路，不解析回答或自动安排评估。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P53" s="9"/>
       <x:c r="Q53" s="9" t="str">
@@ -21428,9 +21456,11 @@
         <x:v>疼痛位置</x:v>
       </x:c>
       <x:c r="C55" s="9" t="str">
-        <x:v>疼在足跟中央还是内侧结节？</x:v>
-      </x:c>
-      <x:c r="D55" s="9"/>
+        <x:v>脚跟底下最痛的是正中间还是偏内侧？</x:v>
+      </x:c>
+      <x:c r="D55" s="9" t="str">
+        <x:v>是一点还是一片？是否向足弓延伸？</x:v>
+      </x:c>
       <x:c r="E55" s="9" t="str">
         <x:v>区分足跟垫中央与筋膜附着处的疼痛范围。</x:v>
       </x:c>
@@ -21463,7 +21493,8 @@
 book://magee-local#pdf=857&amp;print=848</x:v>
       </x:c>
       <x:c r="O55" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P55" s="9"/>
       <x:c r="Q55" s="9"/>
@@ -21476,9 +21507,11 @@
         <x:v>动作与承重</x:v>
       </x:c>
       <x:c r="C56" s="9" t="str">
-        <x:v>赤脚、硬地走路和休息后起步，哪种更明显？</x:v>
-      </x:c>
-      <x:c r="D56" s="9"/>
+        <x:v>赤脚、硬地走路和休息后刚起步，哪种更明显？</x:v>
+      </x:c>
+      <x:c r="D56" s="9" t="str">
+        <x:v>走开后是否减轻？走久后或第二天是否再次加重？</x:v>
+      </x:c>
       <x:c r="E56" s="9" t="str">
         <x:v>了解接触受压与休息后起步的反应差别。</x:v>
       </x:c>
@@ -21511,10 +21544,13 @@
 book://magee-local#pdf=857&amp;print=848</x:v>
       </x:c>
       <x:c r="O56" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P56" s="9"/>
-      <x:c r="Q56" s="9"/>
+      <x:c r="Q56" s="9" t="str">
+        <x:v>QG-PROVOKE</x:v>
+      </x:c>
     </x:row>
     <x:row r="57" ht="112" customHeight="1">
       <x:c r="A57" s="9" t="str">
@@ -21526,7 +21562,9 @@
       <x:c r="C57" s="9" t="str">
         <x:v>有没有突然疼痛、撞击或近期跑跳增加？</x:v>
       </x:c>
-      <x:c r="D57" s="9"/>
+      <x:c r="D57" s="9" t="str">
+        <x:v>是否已有肿胀、夜间或休息时也痛、普通走路明显困难？</x:v>
+      </x:c>
       <x:c r="E57" s="9" t="str">
         <x:v>了解足跟疼痛的外伤或重复负重背景。</x:v>
       </x:c>
@@ -21559,7 +21597,8 @@
 book://magee-local#pdf=857&amp;print=848</x:v>
       </x:c>
       <x:c r="O57" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P57" s="9"/>
       <x:c r="Q57" s="9"/>
@@ -21572,9 +21611,11 @@
         <x:v>疼痛位置</x:v>
       </x:c>
       <x:c r="C58" s="9" t="str">
-        <x:v>疼在足跟起点、足弓中段，还是肌腹附近？</x:v>
-      </x:c>
-      <x:c r="D58" s="9"/>
+        <x:v>脚底不适从脚跟延伸到足弓，还是只在足弓一处？</x:v>
+      </x:c>
+      <x:c r="D58" s="9" t="str">
+        <x:v>有没有麻木、烧灼或向脚趾延伸？</x:v>
+      </x:c>
       <x:c r="E58" s="9" t="str">
         <x:v>区分筋膜起点、足弓中段与邻近肌腹。</x:v>
       </x:c>
@@ -21607,7 +21648,8 @@
 book://magee-local#pdf=857&amp;print=848</x:v>
       </x:c>
       <x:c r="O58" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P58" s="9"/>
       <x:c r="Q58" s="9"/>
@@ -21620,9 +21662,11 @@
         <x:v>动作与承重</x:v>
       </x:c>
       <x:c r="C59" s="9" t="str">
-        <x:v>起步、伸拇趾和持续站走时有什么区别？</x:v>
-      </x:c>
-      <x:c r="D59" s="9"/>
+        <x:v>刚起步、脚趾向上弯和久站走路时，有什么区别？</x:v>
+      </x:c>
+      <x:c r="D59" s="9" t="str">
+        <x:v>脱鞋、换鞋或休息后是否改变？</x:v>
+      </x:c>
       <x:c r="E59" s="9" t="str">
         <x:v>比较起步、筋膜牵拉和持续承重的反应。</x:v>
       </x:c>
@@ -21655,10 +21699,13 @@
 book://magee-local#pdf=857&amp;print=848</x:v>
       </x:c>
       <x:c r="O59" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P59" s="9"/>
-      <x:c r="Q59" s="9"/>
+      <x:c r="Q59" s="9" t="str">
+        <x:v>QG-PROVOKE</x:v>
+      </x:c>
     </x:row>
     <x:row r="60" ht="112" customHeight="1">
       <x:c r="A60" s="9" t="str">
@@ -21716,9 +21763,11 @@
         <x:v>疼痛位置</x:v>
       </x:c>
       <x:c r="C61" s="9" t="str">
-        <x:v>疼在舟骨骨面、内侧突起还是肌腱附近？</x:v>
-      </x:c>
-      <x:c r="D61" s="9"/>
+        <x:v>足弓内侧最突出的位置痛，还是脚背偏内侧或突起后面痛？</x:v>
+      </x:c>
+      <x:c r="D61" s="9" t="str">
+        <x:v>这个突起一直有还是最近出现？鞋子是否压到它？</x:v>
+      </x:c>
       <x:c r="E61" s="9" t="str">
         <x:v>区分舟骨骨面、内侧突起与胫骨后肌腱附近。</x:v>
       </x:c>
@@ -21751,7 +21800,8 @@
 book://magee-local#pdf=857&amp;print=848</x:v>
       </x:c>
       <x:c r="O61" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P61" s="9"/>
       <x:c r="Q61" s="9"/>
@@ -21764,9 +21814,11 @@
         <x:v>动作与承重</x:v>
       </x:c>
       <x:c r="C62" s="9" t="str">
-        <x:v>内翻发力、提踵与鞋具摩擦时有什么区别？</x:v>
-      </x:c>
-      <x:c r="D62" s="9"/>
+        <x:v>脚向内转、踮脚和鞋子摩擦时，有什么区别？</x:v>
+      </x:c>
+      <x:c r="D62" s="9" t="str">
+        <x:v>走久后是否更明显？足弓外形或支撑感有无变化？</x:v>
+      </x:c>
       <x:c r="E62" s="9" t="str">
         <x:v>比较肌腱发力承载与鞋具接触的反应。</x:v>
       </x:c>
@@ -21799,10 +21851,13 @@
 book://magee-local#pdf=857&amp;print=848</x:v>
       </x:c>
       <x:c r="O62" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P62" s="9"/>
-      <x:c r="Q62" s="9"/>
+      <x:c r="Q62" s="9" t="str">
+        <x:v>QG-PROVOKE</x:v>
+      </x:c>
     </x:row>
     <x:row r="63" ht="112" customHeight="1">
       <x:c r="A63" s="9" t="str">
@@ -21860,9 +21915,11 @@
         <x:v>疼痛位置</x:v>
       </x:c>
       <x:c r="C64" s="9" t="str">
-        <x:v>疼在骨头上还是外侧肌腱附近？</x:v>
-      </x:c>
-      <x:c r="D64" s="9"/>
+        <x:v>足外侧突出的骨头附近痛，还是沿外踝后方一路痛下来？</x:v>
+      </x:c>
+      <x:c r="D64" s="9" t="str">
+        <x:v>能否指出最明显的一点？</x:v>
+      </x:c>
       <x:c r="E64" s="9" t="str">
         <x:v>区分第五跖骨骨面与腓骨肌腱附近。</x:v>
       </x:c>
@@ -21895,7 +21952,8 @@
 book://magee-local#pdf=857&amp;print=848</x:v>
       </x:c>
       <x:c r="O64" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P64" s="9"/>
       <x:c r="Q64" s="9"/>
@@ -21943,10 +22001,13 @@
 book://magee-local#pdf=857&amp;print=848</x:v>
       </x:c>
       <x:c r="O65" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P65" s="9"/>
-      <x:c r="Q65" s="9"/>
+      <x:c r="Q65" s="9" t="str">
+        <x:v>QG-PROVOKE</x:v>
+      </x:c>
     </x:row>
     <x:row r="66" ht="112" customHeight="1">
       <x:c r="A66" s="9" t="str">
@@ -21958,7 +22019,9 @@
       <x:c r="C66" s="9" t="str">
         <x:v>是崴脚后出现，还是跑跳增加后逐渐疼？</x:v>
       </x:c>
-      <x:c r="D66" s="9"/>
+      <x:c r="D66" s="9" t="str">
+        <x:v>受伤后能否正常走路？有没有明显肿胀或瘀斑？</x:v>
+      </x:c>
       <x:c r="E66" s="9" t="str">
         <x:v>了解外侧足痛的急性扭伤或重复负重背景。</x:v>
       </x:c>
@@ -21991,7 +22054,8 @@
 book://magee-local#pdf=857&amp;print=848</x:v>
       </x:c>
       <x:c r="O66" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P66" s="9"/>
       <x:c r="Q66" s="9"/>
@@ -22004,9 +22068,11 @@
         <x:v>疼痛位置</x:v>
       </x:c>
       <x:c r="C67" s="9" t="str">
-        <x:v>疼在关节缝、肌腱走行还是鞋带压住的位置？</x:v>
-      </x:c>
-      <x:c r="D67" s="9"/>
+        <x:v>脚背中间最痛在哪里？松开鞋带后会不会好一些？</x:v>
+      </x:c>
+      <x:c r="D67" s="9" t="str">
+        <x:v>是一点、沿一条线，还是较深的一片？</x:v>
+      </x:c>
       <x:c r="E67" s="9" t="str">
         <x:v>区分中足关节线、伸肌腱和鞋带接触区。</x:v>
       </x:c>
@@ -22039,7 +22105,8 @@
 book://magee-local#pdf=857&amp;print=848</x:v>
       </x:c>
       <x:c r="O67" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P67" s="9"/>
       <x:c r="Q67" s="9"/>
@@ -22087,10 +22154,13 @@
 book://magee-local#pdf=857&amp;print=848</x:v>
       </x:c>
       <x:c r="O68" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P68" s="9"/>
-      <x:c r="Q68" s="9"/>
+      <x:c r="Q68" s="9" t="str">
+        <x:v>QG-PROVOKE</x:v>
+      </x:c>
     </x:row>
     <x:row r="69" ht="112" customHeight="1">
       <x:c r="A69" s="9" t="str">
@@ -22102,7 +22172,9 @@
       <x:c r="C69" s="9" t="str">
         <x:v>有没有足部扭转、肿胀或足底瘀斑？</x:v>
       </x:c>
-      <x:c r="D69" s="9"/>
+      <x:c r="D69" s="9" t="str">
+        <x:v>受伤后还能正常走路吗？肿胀是否迅速增加？</x:v>
+      </x:c>
       <x:c r="E69" s="9" t="str">
         <x:v>了解中足外伤及稳定结构评估背景。</x:v>
       </x:c>
@@ -22110,7 +22182,7 @@
         <x:v>足部扭转、肿胀和足底瘀斑经过。</x:v>
       </x:c>
       <x:c r="G69" s="9" t="str">
-        <x:v>可补跗跖稳定结构、骨面与医学评估方向。</x:v>
+        <x:v>中足扭伤后足底瘀斑、明显肿胀或负重困难，需优先医学评估骨性与跗跖稳定结构；暂缓负重旋转和跳跃测试。</x:v>
       </x:c>
       <x:c r="H69" s="9" t="str">
         <x:v>REGION</x:v>
@@ -22132,10 +22204,12 @@
       </x:c>
       <x:c r="N69" s="9" t="str">
         <x:v>baseline://clinical-extension/ConsultationGuide/QG-AF-R-010-3
-book://magee-local#pdf=857&amp;print=848</x:v>
+book://magee-local#pdf=857&amp;print=848
+https://www.orthoinfo.org/diseases--conditions/lisfranc-midfoot-injury</x:v>
       </x:c>
       <x:c r="O69" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P69" s="9"/>
       <x:c r="Q69" s="9"/>
@@ -22150,7 +22224,9 @@
       <x:c r="C70" s="9" t="str">
         <x:v>疼集中在哪个趾根部？有没有像踩到小石子的感觉？</x:v>
       </x:c>
-      <x:c r="D70" s="9"/>
+      <x:c r="D70" s="9" t="str">
+        <x:v>是否有烧灼、麻刺或延伸到相邻脚趾？窄鞋或脱鞋后有何变化？</x:v>
+      </x:c>
       <x:c r="E70" s="9" t="str">
         <x:v>明确前足跖侧疼痛所在趾根。</x:v>
       </x:c>
@@ -22183,7 +22259,8 @@
 book://magee-local#pdf=857&amp;print=848</x:v>
       </x:c>
       <x:c r="O70" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P70" s="9"/>
       <x:c r="Q70" s="9"/>
@@ -22198,7 +22275,9 @@
       <x:c r="C71" s="9" t="str">
         <x:v>前足负重、提踵和鞋底软硬时有什么区别？</x:v>
       </x:c>
-      <x:c r="D71" s="9"/>
+      <x:c r="D71" s="9" t="str">
+        <x:v>走路蹬地、赤脚或穿不同鞋时，疼痛位置是否一致？</x:v>
+      </x:c>
       <x:c r="E71" s="9" t="str">
         <x:v>了解跖骨头承重与鞋底接触的差别。</x:v>
       </x:c>
@@ -22231,10 +22310,13 @@
 book://magee-local#pdf=857&amp;print=848</x:v>
       </x:c>
       <x:c r="O71" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P71" s="9"/>
-      <x:c r="Q71" s="9"/>
+      <x:c r="Q71" s="9" t="str">
+        <x:v>QG-PROVOKE</x:v>
+      </x:c>
     </x:row>
     <x:row r="72" ht="112" customHeight="1">
       <x:c r="A72" s="9" t="str">
@@ -22292,9 +22374,11 @@
         <x:v>疼痛位置</x:v>
       </x:c>
       <x:c r="C73" s="9" t="str">
-        <x:v>疼在关节上方、两侧还是跖侧籽骨附近？</x:v>
-      </x:c>
-      <x:c r="D73" s="9"/>
+        <x:v>大脚趾根部是上面、两侧，还是脚底下面疼？</x:v>
+      </x:c>
+      <x:c r="D73" s="9" t="str">
+        <x:v>与鞋接触处是否相同？突然红、肿、热或静息剧痛也要了解。</x:v>
+      </x:c>
       <x:c r="E73" s="9" t="str">
         <x:v>区分拇趾关节周围与跖侧籽骨区域。</x:v>
       </x:c>
@@ -22327,7 +22411,8 @@
 book://magee-local#pdf=857&amp;print=848</x:v>
       </x:c>
       <x:c r="O73" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P73" s="9"/>
       <x:c r="Q73" s="9"/>
@@ -22340,9 +22425,11 @@
         <x:v>动作与承重</x:v>
       </x:c>
       <x:c r="C74" s="9" t="str">
-        <x:v>拇趾伸展、蹬地与鞋面压迫时有什么区别？</x:v>
-      </x:c>
-      <x:c r="D74" s="9"/>
+        <x:v>大脚趾向上弯、走路蹬地和鞋面压住时，有什么区别？</x:v>
+      </x:c>
+      <x:c r="D74" s="9" t="str">
+        <x:v>是疼痛先限制动作，还是觉得硬卡住？</x:v>
+      </x:c>
       <x:c r="E74" s="9" t="str">
         <x:v>比较拇趾伸展、蹬地与鞋面接触。</x:v>
       </x:c>
@@ -22375,10 +22462,13 @@
 book://magee-local#pdf=857&amp;print=848</x:v>
       </x:c>
       <x:c r="O74" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P74" s="9"/>
-      <x:c r="Q74" s="9"/>
+      <x:c r="Q74" s="9" t="str">
+        <x:v>QG-PROVOKE</x:v>
+      </x:c>
     </x:row>
     <x:row r="75" ht="112" customHeight="1">
       <x:c r="A75" s="9" t="str">
@@ -22436,9 +22526,11 @@
         <x:v>疼痛位置</x:v>
       </x:c>
       <x:c r="C76" s="9" t="str">
-        <x:v>疼在肌腹、肌腱附近还是深部？</x:v>
-      </x:c>
-      <x:c r="D76" s="9"/>
+        <x:v>大腿前面最不舒服的位置在哪里？靠近髋、大腿中段还是膝盖上方？</x:v>
+      </x:c>
+      <x:c r="D76" s="9" t="str">
+        <x:v>是表面一片、深处还是一个明确点？</x:v>
+      </x:c>
       <x:c r="E76" s="9" t="str">
         <x:v>区分大腿前侧肌腹、肌腱与深部区域。</x:v>
       </x:c>
@@ -22471,7 +22563,8 @@
 book://magee-local#pdf=751,756&amp;print=742,747</x:v>
       </x:c>
       <x:c r="O76" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P76" s="9"/>
       <x:c r="Q76" s="9"/>
@@ -22484,9 +22577,11 @@
         <x:v>动作与承重</x:v>
       </x:c>
       <x:c r="C77" s="9" t="str">
-        <x:v>膝屈拉长、伸膝发力和跑跳时有什么区别？</x:v>
-      </x:c>
-      <x:c r="D77" s="9"/>
+        <x:v>弯膝拉伸、踢直膝盖、走路或跑跳时，哪种更明显？</x:v>
+      </x:c>
+      <x:c r="D77" s="9" t="str">
+        <x:v>上下台阶或加速时如何？不要为回答问题现场强行复现疼痛。</x:v>
+      </x:c>
       <x:c r="E77" s="9" t="str">
         <x:v>比较股四头肌牵拉、发力与跑跳承载。</x:v>
       </x:c>
@@ -22519,10 +22614,13 @@
 book://magee-local#pdf=751,756&amp;print=742,747</x:v>
       </x:c>
       <x:c r="O77" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P77" s="9"/>
-      <x:c r="Q77" s="9"/>
+      <x:c r="Q77" s="9" t="str">
+        <x:v>QG-PROVOKE</x:v>
+      </x:c>
     </x:row>
     <x:row r="78" ht="112" customHeight="1">
       <x:c r="A78" s="9" t="str">
@@ -22580,9 +22678,11 @@
         <x:v>疼痛位置</x:v>
       </x:c>
       <x:c r="C79" s="9" t="str">
-        <x:v>疼在后侧肌腹、近端还是膝后肌腱？</x:v>
-      </x:c>
-      <x:c r="D79" s="9"/>
+        <x:v>大腿后面是靠近臀下、肌肉中段，还是膝盖后面疼？</x:v>
+      </x:c>
+      <x:c r="D79" s="9" t="str">
+        <x:v>坐着是否明显？有没有往小腿延伸的麻或电击感？</x:v>
+      </x:c>
       <x:c r="E79" s="9" t="str">
         <x:v>区分后大腿肌腹、近端和远端肌腱。</x:v>
       </x:c>
@@ -22615,7 +22715,8 @@
 book://magee-local#pdf=751,756&amp;print=742,747</x:v>
       </x:c>
       <x:c r="O79" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P79" s="9"/>
       <x:c r="Q79" s="9"/>
@@ -22628,9 +22729,11 @@
         <x:v>动作与承重</x:v>
       </x:c>
       <x:c r="C80" s="9" t="str">
-        <x:v>伸膝牵拉、屈膝发力和快跑时有什么区别？</x:v>
-      </x:c>
-      <x:c r="D80" s="9"/>
+        <x:v>伸直腿拉伸、弯膝发力和快跑时，有什么区别？</x:v>
+      </x:c>
+      <x:c r="D80" s="9" t="str">
+        <x:v>加速、跨大步与减速时是否不同？</x:v>
+      </x:c>
       <x:c r="E80" s="9" t="str">
         <x:v>比较腘绳肌牵拉、膝屈发力与快跑需求。</x:v>
       </x:c>
@@ -22663,10 +22766,13 @@
 book://magee-local#pdf=751,756&amp;print=742,747</x:v>
       </x:c>
       <x:c r="O80" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P80" s="9"/>
-      <x:c r="Q80" s="9"/>
+      <x:c r="Q80" s="9" t="str">
+        <x:v>QG-PROVOKE</x:v>
+      </x:c>
     </x:row>
     <x:row r="81" ht="112" customHeight="1">
       <x:c r="A81" s="9" t="str">
@@ -22724,9 +22830,11 @@
         <x:v>疼痛位置</x:v>
       </x:c>
       <x:c r="C82" s="9" t="str">
-        <x:v>疼在肌腹、近端深层还是膝内侧止点？</x:v>
-      </x:c>
-      <x:c r="D82" s="9"/>
+        <x:v>大腿内侧最痛在上端、中间，还是接近膝下内侧？</x:v>
+      </x:c>
+      <x:c r="D82" s="9" t="str">
+        <x:v>是局部疼，还是从近端延伸下来？</x:v>
+      </x:c>
       <x:c r="E82" s="9" t="str">
         <x:v>区分内侧肌腹、近端深部与膝内侧止点。</x:v>
       </x:c>
@@ -22759,7 +22867,8 @@
 book://magee-local#pdf=751,756&amp;print=742,747</x:v>
       </x:c>
       <x:c r="O82" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P82" s="9"/>
       <x:c r="Q82" s="9"/>
@@ -22772,9 +22881,11 @@
         <x:v>动作与承重</x:v>
       </x:c>
       <x:c r="C83" s="9" t="str">
-        <x:v>外展拉长、内收发力和侧向移动时有什么区别？</x:v>
-      </x:c>
-      <x:c r="D83" s="9"/>
+        <x:v>双腿分开、夹腿、跨步或侧向移动时，哪种会不舒服？</x:v>
+      </x:c>
+      <x:c r="D83" s="9" t="str">
+        <x:v>变向与直线走跑时有何差别？</x:v>
+      </x:c>
       <x:c r="E83" s="9" t="str">
         <x:v>比较内收肌群牵拉、发力及侧向承重。</x:v>
       </x:c>
@@ -22807,10 +22918,13 @@
 book://magee-local#pdf=751,756&amp;print=742,747</x:v>
       </x:c>
       <x:c r="O83" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P83" s="9"/>
-      <x:c r="Q83" s="9"/>
+      <x:c r="Q83" s="9" t="str">
+        <x:v>QG-PROVOKE</x:v>
+      </x:c>
     </x:row>
     <x:row r="84" ht="112" customHeight="1">
       <x:c r="A84" s="9" t="str">
@@ -22868,9 +22982,11 @@
         <x:v>疼痛位置</x:v>
       </x:c>
       <x:c r="C85" s="9" t="str">
-        <x:v>疼在近端肌腹、中段外侧还是膝外侧？</x:v>
-      </x:c>
-      <x:c r="D85" s="9"/>
+        <x:v>大腿外侧最明显的是上段、中段还是接近膝外侧？</x:v>
+      </x:c>
+      <x:c r="D85" s="9" t="str">
+        <x:v>是深部疼、表面麻，还是沿一段延伸？</x:v>
+      </x:c>
       <x:c r="E85" s="9" t="str">
         <x:v>区分近端肌腹、外侧中段和膝外侧。</x:v>
       </x:c>
@@ -22903,7 +23019,8 @@
 book://magee-local#pdf=751,756&amp;print=742,747</x:v>
       </x:c>
       <x:c r="O85" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P85" s="9"/>
       <x:c r="Q85" s="9"/>
@@ -22951,10 +23068,13 @@
 book://magee-local#pdf=751,756&amp;print=742,747</x:v>
       </x:c>
       <x:c r="O86" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P86" s="9"/>
-      <x:c r="Q86" s="9"/>
+      <x:c r="Q86" s="9" t="str">
+        <x:v>QG-PROVOKE</x:v>
+      </x:c>
     </x:row>
     <x:row r="87" ht="112" customHeight="1">
       <x:c r="A87" s="9" t="str">
@@ -23013,9 +23133,11 @@
         <x:v>疼痛位置</x:v>
       </x:c>
       <x:c r="C88" s="9" t="str">
-        <x:v>疼在髌骨周围、髌骨上下缘肌腱，还是胫骨结节？</x:v>
-      </x:c>
-      <x:c r="D88" s="9"/>
+        <x:v>膝盖前面最痛在哪里？髌骨周围、上缘、下缘还是更下方的骨头突起？</x:v>
+      </x:c>
+      <x:c r="D88" s="9" t="str">
+        <x:v>能用手指出最明显位置吗？跪地接触痛与运动痛在同一处吗？</x:v>
+      </x:c>
       <x:c r="E88" s="9" t="str">
         <x:v>区分髌周、上下缘肌腱与胫骨结节。</x:v>
       </x:c>
@@ -23048,7 +23170,8 @@
 book://magee-local#pdf=739&amp;print=730</x:v>
       </x:c>
       <x:c r="O88" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P88" s="9"/>
       <x:c r="Q88" s="9"/>
@@ -23096,10 +23219,13 @@
 book://magee-local#pdf=739&amp;print=730</x:v>
       </x:c>
       <x:c r="O89" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P89" s="9"/>
-      <x:c r="Q89" s="9"/>
+      <x:c r="Q89" s="9" t="str">
+        <x:v>QG-PROVOKE</x:v>
+      </x:c>
     </x:row>
     <x:row r="90" ht="112" customHeight="1">
       <x:c r="A90" s="9" t="str">
@@ -23109,9 +23235,11 @@
         <x:v>外伤与变化</x:v>
       </x:c>
       <x:c r="C90" s="9" t="str">
-        <x:v>有没有扭转、撞击、突然肿胀、真正卡住或明显失稳？</x:v>
-      </x:c>
-      <x:c r="D90" s="9"/>
+        <x:v>有没有扭伤、撞击、突然肿胀，或髌骨滑出去的感觉？</x:v>
+      </x:c>
+      <x:c r="D90" s="9" t="str">
+        <x:v>所谓卡住是关节确实动不了，还是怕痛不敢动？有无突然不能主动伸直膝盖？</x:v>
+      </x:c>
       <x:c r="E90" s="9" t="str">
         <x:v>了解膝前外伤和伸膝装置评估背景。</x:v>
       </x:c>
@@ -23144,7 +23272,8 @@
 book://magee-local#pdf=739&amp;print=730</x:v>
       </x:c>
       <x:c r="O90" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P90" s="9"/>
       <x:c r="Q90" s="9"/>
@@ -23157,9 +23286,11 @@
         <x:v>疼痛位置</x:v>
       </x:c>
       <x:c r="C91" s="9" t="str">
-        <x:v>疼在内侧关节线、韧带走行、下方鹅足，还是后内侧肌腱附近？</x:v>
-      </x:c>
-      <x:c r="D91" s="9"/>
+        <x:v>膝内侧最痛在关节缝附近、膝下内侧，还是偏后方？</x:v>
+      </x:c>
+      <x:c r="D91" s="9" t="str">
+        <x:v>范围是一点还是沿一段？</x:v>
+      </x:c>
       <x:c r="E91" s="9" t="str">
         <x:v>区分内侧关节线、韧带、鹅足及后内侧肌腱。</x:v>
       </x:c>
@@ -23192,7 +23323,8 @@
 book://magee-local#pdf=739&amp;print=730</x:v>
       </x:c>
       <x:c r="O91" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P91" s="9"/>
       <x:c r="Q91" s="9"/>
@@ -23205,9 +23337,11 @@
         <x:v>动作反应</x:v>
       </x:c>
       <x:c r="C92" s="9" t="str">
-        <x:v>伸屈膝、内收或屈膝发力时有什么区别？</x:v>
-      </x:c>
-      <x:c r="D92" s="9"/>
+        <x:v>上下台阶、转身、弯膝或夹腿时，哪种会不舒服？</x:v>
+      </x:c>
+      <x:c r="D92" s="9" t="str">
+        <x:v>日常活动中是否有膝向内偏或被外力推向内侧的受伤经过？</x:v>
+      </x:c>
       <x:c r="E92" s="9" t="str">
         <x:v>比较关节活动、内收和膝屈发力。</x:v>
       </x:c>
@@ -23240,10 +23374,13 @@
 book://magee-local#pdf=739&amp;print=730</x:v>
       </x:c>
       <x:c r="O92" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P92" s="9"/>
-      <x:c r="Q92" s="9"/>
+      <x:c r="Q92" s="9" t="str">
+        <x:v>QG-PROVOKE</x:v>
+      </x:c>
     </x:row>
     <x:row r="93" ht="112" customHeight="1">
       <x:c r="A93" s="9" t="str">
@@ -23253,9 +23390,11 @@
         <x:v>外伤与变化</x:v>
       </x:c>
       <x:c r="C93" s="9" t="str">
-        <x:v>有没有扭转、撞击、突然肿胀、真正卡住或明显失稳？</x:v>
-      </x:c>
-      <x:c r="D93" s="9"/>
+        <x:v>这次是否在转身、扭膝或受到侧向撞击后开始？</x:v>
+      </x:c>
+      <x:c r="D93" s="9" t="str">
+        <x:v>何时开始肿？是否真正卡住无法伸屈，或反复有失控打软的感觉？</x:v>
+      </x:c>
       <x:c r="E93" s="9" t="str">
         <x:v>了解内侧膝痛的扭转和撞击经过。</x:v>
       </x:c>
@@ -23288,7 +23427,8 @@
 book://magee-local#pdf=739&amp;print=730</x:v>
       </x:c>
       <x:c r="O93" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P93" s="9"/>
       <x:c r="Q93" s="9"/>
@@ -23301,9 +23441,11 @@
         <x:v>疼痛位置</x:v>
       </x:c>
       <x:c r="C94" s="9" t="str">
-        <x:v>疼在外侧关节线、腓骨头还是外侧肌腱附近？</x:v>
-      </x:c>
-      <x:c r="D94" s="9"/>
+        <x:v>膝外侧疼在关节缝、稍上方，还是膝下外侧骨头突起附近？</x:v>
+      </x:c>
+      <x:c r="D94" s="9" t="str">
+        <x:v>是否延伸到小腿或足背？</x:v>
+      </x:c>
       <x:c r="E94" s="9" t="str">
         <x:v>区分外侧关节线、腓骨头与外侧肌腱。</x:v>
       </x:c>
@@ -23336,7 +23478,8 @@
 book://magee-local#pdf=739&amp;print=730</x:v>
       </x:c>
       <x:c r="O94" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P94" s="9"/>
       <x:c r="Q94" s="9"/>
@@ -23349,9 +23492,11 @@
         <x:v>动作反应</x:v>
       </x:c>
       <x:c r="C95" s="9" t="str">
-        <x:v>屈膝发力、胫骨旋转和跑步时有什么区别？</x:v>
-      </x:c>
-      <x:c r="D95" s="9"/>
+        <x:v>弯膝、转身、跑步或下坡时，有什么区别？</x:v>
+      </x:c>
+      <x:c r="D95" s="9" t="str">
+        <x:v>是否总在相近距离或屈膝角度出现？</x:v>
+      </x:c>
       <x:c r="E95" s="9" t="str">
         <x:v>比较膝屈发力、旋转与跑步反应。</x:v>
       </x:c>
@@ -23384,10 +23529,13 @@
 book://magee-local#pdf=739&amp;print=730</x:v>
       </x:c>
       <x:c r="O95" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P95" s="9"/>
-      <x:c r="Q95" s="9"/>
+      <x:c r="Q95" s="9" t="str">
+        <x:v>QG-PROVOKE</x:v>
+      </x:c>
     </x:row>
     <x:row r="96" ht="112" customHeight="1">
       <x:c r="A96" s="9" t="str">
@@ -23397,9 +23545,11 @@
         <x:v>外伤与变化</x:v>
       </x:c>
       <x:c r="C96" s="9" t="str">
-        <x:v>有没有扭转、撞击、突然肿胀、真正卡住或明显失稳？</x:v>
-      </x:c>
-      <x:c r="D96" s="9"/>
+        <x:v>有没有扭转、侧向撞击，或突然踩空的受伤经过？</x:v>
+      </x:c>
+      <x:c r="D96" s="9" t="str">
+        <x:v>有没有肿胀、真正卡住、失控打软，或足背麻木、抬脚无力？</x:v>
+      </x:c>
       <x:c r="E96" s="9" t="str">
         <x:v>了解外侧膝痛的受伤机制与变化。</x:v>
       </x:c>
@@ -23432,7 +23582,8 @@
 book://magee-local#pdf=739&amp;print=730</x:v>
       </x:c>
       <x:c r="O96" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P96" s="9"/>
       <x:c r="Q96" s="9"/>
@@ -23445,9 +23596,11 @@
         <x:v>疼痛位置</x:v>
       </x:c>
       <x:c r="C97" s="9" t="str">
-        <x:v>疼在腘窝中央、后内侧肌腱还是后外侧肌腹？</x:v>
-      </x:c>
-      <x:c r="D97" s="9"/>
+        <x:v>膝后是正中间、内侧还是外侧疼？</x:v>
+      </x:c>
+      <x:c r="D97" s="9" t="str">
+        <x:v>有没有摸到包块？是否向小腿延伸？</x:v>
+      </x:c>
       <x:c r="E97" s="9" t="str">
         <x:v>区分腘窝中央与后内外侧肌腱/肌腹。</x:v>
       </x:c>
@@ -23480,7 +23633,8 @@
 book://magee-local#pdf=739&amp;print=730</x:v>
       </x:c>
       <x:c r="O97" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P97" s="9"/>
       <x:c r="Q97" s="9"/>
@@ -23493,9 +23647,11 @@
         <x:v>动作反应</x:v>
       </x:c>
       <x:c r="C98" s="9" t="str">
-        <x:v>伸膝牵拉、屈膝发力与提踵时有什么区别？</x:v>
-      </x:c>
-      <x:c r="D98" s="9"/>
+        <x:v>伸直膝盖、弯膝发力或踮脚时，哪种更明显？</x:v>
+      </x:c>
+      <x:c r="D98" s="9" t="str">
+        <x:v>是拉长时不适、发力痛，还是膝盖里顶胀？</x:v>
+      </x:c>
       <x:c r="E98" s="9" t="str">
         <x:v>比较后侧牵拉、膝屈发力与跖屈承载。</x:v>
       </x:c>
@@ -23528,10 +23684,13 @@
 book://magee-local#pdf=739&amp;print=730</x:v>
       </x:c>
       <x:c r="O98" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P98" s="9"/>
-      <x:c r="Q98" s="9"/>
+      <x:c r="Q98" s="9" t="str">
+        <x:v>QG-PROVOKE</x:v>
+      </x:c>
     </x:row>
     <x:row r="99" ht="112" customHeight="1">
       <x:c r="A99" s="9" t="str">
@@ -23541,9 +23700,11 @@
         <x:v>外伤与变化</x:v>
       </x:c>
       <x:c r="C99" s="9" t="str">
-        <x:v>有没有扭转、撞击、突然肿胀、真正卡住或明显失稳？</x:v>
-      </x:c>
-      <x:c r="D99" s="9"/>
+        <x:v>有没有突然拉扯、扭伤、膝后包块或小腿肿胀？</x:v>
+      </x:c>
+      <x:c r="D99" s="9" t="str">
+        <x:v>是否伴发热、变色？膝盖是否真正卡住？</x:v>
+      </x:c>
       <x:c r="E99" s="9" t="str">
         <x:v>了解膝后外伤、肿胀与活动阻挡。</x:v>
       </x:c>
@@ -23551,7 +23712,7 @@
         <x:v>扭转、撞击、肿胀时机、卡锁和失稳经过。</x:v>
       </x:c>
       <x:c r="G99" s="9" t="str">
-        <x:v>可补膝后稳定结构、关节内反应及腘窝局部评估。</x:v>
+        <x:v>结合膝后包块、关节与肌腱检查；新发单侧小腿明显肿热应先医学评估，不以一次牵拉反应排除血管问题。</x:v>
       </x:c>
       <x:c r="H99" s="9" t="str">
         <x:v>REGION</x:v>
@@ -23576,7 +23737,8 @@
 book://magee-local#pdf=739&amp;print=730</x:v>
       </x:c>
       <x:c r="O99" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P99" s="9"/>
       <x:c r="Q99" s="9"/>
@@ -23672,10 +23834,13 @@
 book://magee-local#pdf=739&amp;print=730</x:v>
       </x:c>
       <x:c r="O101" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P101" s="9"/>
-      <x:c r="Q101" s="9"/>
+      <x:c r="Q101" s="9" t="str">
+        <x:v>QG-PROVOKE</x:v>
+      </x:c>
     </x:row>
     <x:row r="102" ht="112" customHeight="1">
       <x:c r="A102" s="9" t="str">
@@ -23685,9 +23850,11 @@
         <x:v>外伤与变化</x:v>
       </x:c>
       <x:c r="C102" s="9" t="str">
-        <x:v>有没有扭转、撞击、突然肿胀、真正卡住或明显失稳？</x:v>
-      </x:c>
-      <x:c r="D102" s="9"/>
+        <x:v>有没有明显外伤，或没有外伤也突然肿、热？</x:v>
+      </x:c>
+      <x:c r="D102" s="9" t="str">
+        <x:v>是整圈胀、反复积液，还是伸屈确实受阻？有没有发热或其他关节同时不适？</x:v>
+      </x:c>
       <x:c r="E102" s="9" t="str">
         <x:v>了解膝周症状的外伤与关节变化背景。</x:v>
       </x:c>
@@ -23695,7 +23862,7 @@
         <x:v>扭转、撞击、肿胀、卡锁及失稳经过。</x:v>
       </x:c>
       <x:c r="G102" s="9" t="str">
-        <x:v>可补关节积液、完整性和稳定性评估方向。</x:v>
+        <x:v>结合关节积液、活动受限与全身表现；急性红肿热伴发热、明显负重困难等应先医学评估。</x:v>
       </x:c>
       <x:c r="H102" s="9" t="str">
         <x:v>REGION</x:v>
@@ -23720,10 +23887,1434 @@
 book://magee-local#pdf=739&amp;print=730</x:v>
       </x:c>
       <x:c r="O102" s="9" t="str">
-        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。</x:v>
+        <x:v>产品编辑按本问题及区域解剖整理用途，教材支持问诊与检查框架，不是教材原文或经验证的分诊规则。仅展示问诊思路，不录入回答，不自动确定组织、诊断或训练。
+2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
       </x:c>
       <x:c r="P102" s="9"/>
       <x:c r="Q102" s="9"/>
+    </x:row>
+    <x:row r="103" ht="170" customHeight="1">
+      <x:c r="A103" s="19" t="str">
+        <x:v>QG-PAIN-QUALITY</x:v>
+      </x:c>
+      <x:c r="B103" s="19" t="str">
+        <x:v>疼痛性质与分布</x:v>
+      </x:c>
+      <x:c r="C103" s="19" t="str">
+        <x:v>这种不舒服是什么感觉？请先用自己的话描述。</x:v>
+      </x:c>
+      <x:c r="D103" s="19" t="str">
+        <x:v>描述困难时，可询问酸胀、钝痛、针刺、烧灼、电击、拉扯或卡压等；是否伴麻木、轻碰痛或向其他位置延伸？</x:v>
+      </x:c>
+      <x:c r="E103" s="19" t="str">
+        <x:v>了解体验、范围及伴随感觉，减少仅凭疼痛位置推断组织的偏差。</x:v>
+      </x:c>
+      <x:c r="F103" s="19" t="str">
+        <x:v>疼痛性质、是否混合出现、放射范围及感觉变化。</x:v>
+      </x:c>
+      <x:c r="G103" s="19" t="str">
+        <x:v>结合受力反应选择局部检查；麻、电击或烧灼伴合理分布时补神经筛查。描述本身不能确定神经、肌腱或关节病变。</x:v>
+      </x:c>
+      <x:c r="H103" s="19" t="str">
+        <x:v>GENERAL</x:v>
+      </x:c>
+      <x:c r="I103" s="19" t="str">
+        <x:v>KNEE|LOWER_LEG|ANKLE_FOOT|THIGH</x:v>
+      </x:c>
+      <x:c r="J103" s="19"/>
+      <x:c r="K103" s="19" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="L103" s="19" t="str">
+        <x:v>Display_Only</x:v>
+      </x:c>
+      <x:c r="M103" s="19" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="N103" s="19" t="str">
+        <x:v>https://www.iasp-pain.org/resources/fact-sheets/identifying-neuropathic-pain-in-the-clinic-a-guide-for-clinicians/</x:v>
+      </x:c>
+      <x:c r="O103" s="19" t="str">
+        <x:v>2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
+      </x:c>
+      <x:c r="P103" s="19"/>
+      <x:c r="Q103" s="19"/>
+    </x:row>
+    <x:row r="104" ht="170" customHeight="1">
+      <x:c r="A104" s="19" t="str">
+        <x:v>QG-IRRITABILITY</x:v>
+      </x:c>
+      <x:c r="B104" s="19" t="str">
+        <x:v>症状多久恢复</x:v>
+      </x:c>
+      <x:c r="C104" s="19" t="str">
+        <x:v>最容易不舒服的活动，大概做到什么程度开始？停下来后多久恢复？</x:v>
+      </x:c>
+      <x:c r="D104" s="19" t="str">
+        <x:v>当晚或第二天是否比原来更不舒服？有没有休息或睡觉时也痛？可请患者描述能接受的活动范围。</x:v>
+      </x:c>
+      <x:c r="E104" s="19" t="str">
+        <x:v>了解症状敏感程度和恢复过程，决定本次评估的起始负荷。</x:v>
+      </x:c>
+      <x:c r="F104" s="19" t="str">
+        <x:v>诱发所需活动量、缓解时间、延迟反应及静息表现。</x:v>
+      </x:c>
+      <x:c r="G104" s="19" t="str">
+        <x:v>从可耐受、易停止的任务开始，控制重复次数并观察恢复；持续加重或出现异常伴随表现时先调整评估方向。</x:v>
+      </x:c>
+      <x:c r="H104" s="19" t="str">
+        <x:v>GENERAL</x:v>
+      </x:c>
+      <x:c r="I104" s="19" t="str">
+        <x:v>KNEE|LOWER_LEG|ANKLE_FOOT|THIGH</x:v>
+      </x:c>
+      <x:c r="J104" s="19"/>
+      <x:c r="K104" s="19" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="L104" s="19" t="str">
+        <x:v>Display_Only</x:v>
+      </x:c>
+      <x:c r="M104" s="19" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="N104" s="19" t="str">
+        <x:v>https://www.nice.org.uk/guidance/ng193/chapter/recommendations</x:v>
+      </x:c>
+      <x:c r="O104" s="19" t="str">
+        <x:v>2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
+      </x:c>
+      <x:c r="P104" s="19"/>
+      <x:c r="Q104" s="19"/>
+    </x:row>
+    <x:row r="105" ht="170" customHeight="1">
+      <x:c r="A105" s="19" t="str">
+        <x:v>QG-SART-1</x:v>
+      </x:c>
+      <x:c r="B105" s="19" t="str">
+        <x:v>斜行不适的位置</x:v>
+      </x:c>
+      <x:c r="C105" s="19" t="str">
+        <x:v>不适在大腿前内侧哪一段？是否一路延伸到膝下内侧？</x:v>
+      </x:c>
+      <x:c r="D105" s="19" t="str">
+        <x:v>能否指出最明显的一处？</x:v>
+      </x:c>
+      <x:c r="E105" s="19" t="str">
+        <x:v>分清斜行范围与局部最明显点。</x:v>
+      </x:c>
+      <x:c r="F105" s="19" t="str">
+        <x:v>近端、肌腹或远端分布。</x:v>
+      </x:c>
+      <x:c r="G105" s="19" t="str">
+        <x:v>分别查看缝匠肌邻近、内收肌群及鹅足；不能仅凭走向锁定一块肌肉。</x:v>
+      </x:c>
+      <x:c r="H105" s="19" t="str">
+        <x:v>LOCATION</x:v>
+      </x:c>
+      <x:c r="I105" s="19" t="str">
+        <x:v>THIGH</x:v>
+      </x:c>
+      <x:c r="J105" s="19"/>
+      <x:c r="K105" s="19" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L105" s="19" t="str">
+        <x:v>Display_Only</x:v>
+      </x:c>
+      <x:c r="M105" s="19" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="N105" s="19" t="str">
+        <x:v>baseline://clinical-extension/ConsultationGuide/QG-THIGH-R-001-1
+book://magee-local#pdf=751,756&amp;print=742,747</x:v>
+      </x:c>
+      <x:c r="O105" s="19" t="str">
+        <x:v>2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
+      </x:c>
+      <x:c r="P105" s="19" t="str">
+        <x:v>LOC-THIGH-SART</x:v>
+      </x:c>
+      <x:c r="Q105" s="19" t="str">
+        <x:v>QG-THIGH-R-001-1|QG-THIGH-R-003-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="170" customHeight="1">
+      <x:c r="A106" s="19" t="str">
+        <x:v>QG-SART-2</x:v>
+      </x:c>
+      <x:c r="B106" s="19" t="str">
+        <x:v>哪些动作会不舒服</x:v>
+      </x:c>
+      <x:c r="C106" s="19" t="str">
+        <x:v>抬腿、盘腿、弯膝或上下台阶时，有什么区别？</x:v>
+      </x:c>
+      <x:c r="D106" s="19" t="str">
+        <x:v>夹腿与伸直膝盖时也会出现吗？</x:v>
+      </x:c>
+      <x:c r="E106" s="19" t="str">
+        <x:v>比较跨髋膝动作与邻近肌群受力。</x:v>
+      </x:c>
+      <x:c r="F106" s="19" t="str">
+        <x:v>诱发动作与症状位置是否一致。</x:v>
+      </x:c>
+      <x:c r="G106" s="19" t="str">
+        <x:v>对照髋膝组合活动、膝屈与邻近肌群输出。</x:v>
+      </x:c>
+      <x:c r="H106" s="19" t="str">
+        <x:v>LOCATION</x:v>
+      </x:c>
+      <x:c r="I106" s="19" t="str">
+        <x:v>THIGH</x:v>
+      </x:c>
+      <x:c r="J106" s="19"/>
+      <x:c r="K106" s="19" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="L106" s="19" t="str">
+        <x:v>Display_Only</x:v>
+      </x:c>
+      <x:c r="M106" s="19" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="N106" s="19" t="str">
+        <x:v>baseline://clinical-extension/ConsultationGuide/QG-THIGH-R-001-2
+book://magee-local#pdf=751,756&amp;print=742,747</x:v>
+      </x:c>
+      <x:c r="O106" s="19" t="str">
+        <x:v>2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
+      </x:c>
+      <x:c r="P106" s="19" t="str">
+        <x:v>LOC-THIGH-SART</x:v>
+      </x:c>
+      <x:c r="Q106" s="19" t="str">
+        <x:v>QG-THIGH-R-001-2|QG-THIGH-R-003-2|QG-PROVOKE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="170" customHeight="1">
+      <x:c r="A107" s="19" t="str">
+        <x:v>QG-SART-3</x:v>
+      </x:c>
+      <x:c r="B107" s="19" t="str">
+        <x:v>开始经过与伴随表现</x:v>
+      </x:c>
+      <x:c r="C107" s="19" t="str">
+        <x:v>是某次跨步、扭转后突然出现，还是逐渐不适？</x:v>
+      </x:c>
+      <x:c r="D107" s="19" t="str">
+        <x:v>有无瘀斑、肿胀、麻木或取腱手术史？</x:v>
+      </x:c>
+      <x:c r="E107" s="19" t="str">
+        <x:v>补充损伤、手术及感觉背景。</x:v>
+      </x:c>
+      <x:c r="F107" s="19" t="str">
+        <x:v>起病机制、手术范围、感觉变化。</x:v>
+      </x:c>
+      <x:c r="G107" s="19" t="str">
+        <x:v>急性明显损伤先排完整性；感觉异常按分布补神经检查。</x:v>
+      </x:c>
+      <x:c r="H107" s="19" t="str">
+        <x:v>LOCATION</x:v>
+      </x:c>
+      <x:c r="I107" s="19" t="str">
+        <x:v>THIGH</x:v>
+      </x:c>
+      <x:c r="J107" s="19"/>
+      <x:c r="K107" s="19" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L107" s="19" t="str">
+        <x:v>Display_Only</x:v>
+      </x:c>
+      <x:c r="M107" s="19" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="N107" s="19" t="str">
+        <x:v>baseline://clinical-extension/ConsultationGuide/QG-THIGH-R-001-3
+book://magee-local#pdf=751,756&amp;print=742,747</x:v>
+      </x:c>
+      <x:c r="O107" s="19" t="str">
+        <x:v>2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
+      </x:c>
+      <x:c r="P107" s="19" t="str">
+        <x:v>LOC-THIGH-SART</x:v>
+      </x:c>
+      <x:c r="Q107" s="19" t="str">
+        <x:v>QG-THIGH-R-001-3|QG-THIGH-R-003-3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="170" customHeight="1">
+      <x:c r="A108" s="19" t="str">
+        <x:v>QG-PES-1</x:v>
+      </x:c>
+      <x:c r="B108" s="19" t="str">
+        <x:v>膝下内侧的位置</x:v>
+      </x:c>
+      <x:c r="C108" s="19" t="str">
+        <x:v>最痛的是膝内侧关节缝，还是往下几厘米的地方？</x:v>
+      </x:c>
+      <x:c r="D108" s="19" t="str">
+        <x:v>是表面按压不适、深部疼，还是一片烧灼或麻木？</x:v>
+      </x:c>
+      <x:c r="E108" s="19" t="str">
+        <x:v>区分关节线与鹅足附着邻近。</x:v>
+      </x:c>
+      <x:c r="F108" s="19" t="str">
+        <x:v>具体位置、深浅感及伴随感觉。</x:v>
+      </x:c>
+      <x:c r="G108" s="19" t="str">
+        <x:v>对照鹅足肌腱与滑囊邻近、关节线及必要的感觉检查；位置不能单独确认滑囊炎。</x:v>
+      </x:c>
+      <x:c r="H108" s="19" t="str">
+        <x:v>LOCATION</x:v>
+      </x:c>
+      <x:c r="I108" s="19" t="str">
+        <x:v>KNEE</x:v>
+      </x:c>
+      <x:c r="J108" s="19"/>
+      <x:c r="K108" s="19" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L108" s="19" t="str">
+        <x:v>Display_Only</x:v>
+      </x:c>
+      <x:c r="M108" s="19" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="N108" s="19" t="str">
+        <x:v>https://www.orthoinfo.org/diseases--conditions/pes-anserine-knee-tendon-bursitis</x:v>
+      </x:c>
+      <x:c r="O108" s="19" t="str">
+        <x:v>2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
+      </x:c>
+      <x:c r="P108" s="19" t="str">
+        <x:v>LOC-KNEE-R-008</x:v>
+      </x:c>
+      <x:c r="Q108" s="19" t="str">
+        <x:v>QG-KNEE-MEDIAL-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="170" customHeight="1">
+      <x:c r="A109" s="19" t="str">
+        <x:v>QG-PES-2</x:v>
+      </x:c>
+      <x:c r="B109" s="19" t="str">
+        <x:v>上下台阶与屈膝反应</x:v>
+      </x:c>
+      <x:c r="C109" s="19" t="str">
+        <x:v>上下台阶、走久、弯膝或从椅子上起身时，哪种更明显？</x:v>
+      </x:c>
+      <x:c r="D109" s="19" t="str">
+        <x:v>直接压到膝下内侧时，是否和活动时一样？</x:v>
+      </x:c>
+      <x:c r="E109" s="19" t="str">
+        <x:v>比较局部接触与肌腱受力、负重反应。</x:v>
+      </x:c>
+      <x:c r="F109" s="19" t="str">
+        <x:v>诱发任务、接触敏感和疼痛一致性。</x:v>
+      </x:c>
+      <x:c r="G109" s="19" t="str">
+        <x:v>结合鹅足局部检查、膝屈肌输出与步行或台阶观察。</x:v>
+      </x:c>
+      <x:c r="H109" s="19" t="str">
+        <x:v>LOCATION</x:v>
+      </x:c>
+      <x:c r="I109" s="19" t="str">
+        <x:v>KNEE</x:v>
+      </x:c>
+      <x:c r="J109" s="19"/>
+      <x:c r="K109" s="19" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="L109" s="19" t="str">
+        <x:v>Display_Only</x:v>
+      </x:c>
+      <x:c r="M109" s="19" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="N109" s="19" t="str">
+        <x:v>https://www.orthoinfo.org/diseases--conditions/pes-anserine-knee-tendon-bursitis</x:v>
+      </x:c>
+      <x:c r="O109" s="19" t="str">
+        <x:v>2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
+      </x:c>
+      <x:c r="P109" s="19" t="str">
+        <x:v>LOC-KNEE-R-008</x:v>
+      </x:c>
+      <x:c r="Q109" s="19" t="str">
+        <x:v>QG-KNEE-MEDIAL-2|QG-PROVOKE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="170" customHeight="1">
+      <x:c r="A110" s="19" t="str">
+        <x:v>QG-PES-3</x:v>
+      </x:c>
+      <x:c r="B110" s="19" t="str">
+        <x:v>活动变化和受伤经过</x:v>
+      </x:c>
+      <x:c r="C110" s="19" t="str">
+        <x:v>最近走跑或台阶量增加了吗？有没有扭伤或撞击？</x:v>
+      </x:c>
+      <x:c r="D110" s="19" t="str">
+        <x:v>有无鹅足取腱手术史、局部肿热、卡住或打软？</x:v>
+      </x:c>
+      <x:c r="E110" s="19" t="str">
+        <x:v>避免把此处不适一律归于鹅足肌肉。</x:v>
+      </x:c>
+      <x:c r="F110" s="19" t="str">
+        <x:v>负荷、手术及关节伴随表现。</x:v>
+      </x:c>
+      <x:c r="G110" s="19" t="str">
+        <x:v>关节卡锁或不稳另查关节结构；局部明显红肿热先判断是否需医学评估。</x:v>
+      </x:c>
+      <x:c r="H110" s="19" t="str">
+        <x:v>LOCATION</x:v>
+      </x:c>
+      <x:c r="I110" s="19" t="str">
+        <x:v>KNEE</x:v>
+      </x:c>
+      <x:c r="J110" s="19"/>
+      <x:c r="K110" s="19" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L110" s="19" t="str">
+        <x:v>Display_Only</x:v>
+      </x:c>
+      <x:c r="M110" s="19" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="N110" s="19" t="str">
+        <x:v>https://www.orthoinfo.org/diseases--conditions/pes-anserine-knee-tendon-bursitis</x:v>
+      </x:c>
+      <x:c r="O110" s="19" t="str">
+        <x:v>2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
+      </x:c>
+      <x:c r="P110" s="19" t="str">
+        <x:v>LOC-KNEE-R-008</x:v>
+      </x:c>
+      <x:c r="Q110" s="19" t="str">
+        <x:v>QG-KNEE-MEDIAL-3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="170" customHeight="1">
+      <x:c r="A111" s="19" t="str">
+        <x:v>QG-PATELLAR-1</x:v>
+      </x:c>
+      <x:c r="B111" s="19" t="str">
+        <x:v>髌腱附近的位置</x:v>
+      </x:c>
+      <x:c r="C111" s="19" t="str">
+        <x:v>痛在髌骨下缘、下面那条腱，还是更深的膝前方？</x:v>
+      </x:c>
+      <x:c r="D111" s="19" t="str">
+        <x:v>能否指出一个固定点？跪地与发力时位置相同吗？</x:v>
+      </x:c>
+      <x:c r="E111" s="19" t="str">
+        <x:v>分清髌腱、邻近脂肪垫和接触位置。</x:v>
+      </x:c>
+      <x:c r="F111" s="19" t="str">
+        <x:v>疼痛最明显点及位置的一致性。</x:v>
+      </x:c>
+      <x:c r="G111" s="19" t="str">
+        <x:v>与髌腱局部、伸膝输出及髌下邻近组织对照，不凭压痛确诊。</x:v>
+      </x:c>
+      <x:c r="H111" s="19" t="str">
+        <x:v>LOCATION</x:v>
+      </x:c>
+      <x:c r="I111" s="19" t="str">
+        <x:v>KNEE</x:v>
+      </x:c>
+      <x:c r="J111" s="19"/>
+      <x:c r="K111" s="19" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L111" s="19" t="str">
+        <x:v>Display_Only</x:v>
+      </x:c>
+      <x:c r="M111" s="19" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="N111" s="19" t="str">
+        <x:v>baseline://clinical-extension/ConsultationGuide/QG-KNEE-FRONT-1
+book://magee-local#pdf=739&amp;print=730</x:v>
+      </x:c>
+      <x:c r="O111" s="19" t="str">
+        <x:v>2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
+      </x:c>
+      <x:c r="P111" s="19" t="str">
+        <x:v>LOC-KNEE-R-005|LOC-KNEE-PATELLAR-TENDON</x:v>
+      </x:c>
+      <x:c r="Q111" s="19" t="str">
+        <x:v>QG-KNEE-FRONT-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="170" customHeight="1">
+      <x:c r="A112" s="19" t="str">
+        <x:v>QG-PATELLAR-2</x:v>
+      </x:c>
+      <x:c r="B112" s="19" t="str">
+        <x:v>跳跃与伸膝负荷</x:v>
+      </x:c>
+      <x:c r="C112" s="19" t="str">
+        <x:v>跳跃、落地、加速、下台阶时，什么时候疼？</x:v>
+      </x:c>
+      <x:c r="D112" s="19" t="str">
+        <x:v>热身后、活动后和第二天有什么变化？近期训练有没有增加？</x:v>
+      </x:c>
+      <x:c r="E112" s="19" t="str">
+        <x:v>明确伸膝负荷及恢复反应。</x:v>
+      </x:c>
+      <x:c r="F112" s="19" t="str">
+        <x:v>动作阶段、负荷变化和延迟反应。</x:v>
+      </x:c>
+      <x:c r="G112" s="19" t="str">
+        <x:v>从可耐受伸膝或低负荷动作开始，再决定是否需要更高强度任务。</x:v>
+      </x:c>
+      <x:c r="H112" s="19" t="str">
+        <x:v>LOCATION</x:v>
+      </x:c>
+      <x:c r="I112" s="19" t="str">
+        <x:v>KNEE</x:v>
+      </x:c>
+      <x:c r="J112" s="19"/>
+      <x:c r="K112" s="19" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="L112" s="19" t="str">
+        <x:v>Display_Only</x:v>
+      </x:c>
+      <x:c r="M112" s="19" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="N112" s="19" t="str">
+        <x:v>baseline://clinical-extension/ConsultationGuide/QG-KNEE-FRONT-2
+book://magee-local#pdf=739&amp;print=730</x:v>
+      </x:c>
+      <x:c r="O112" s="19" t="str">
+        <x:v>2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
+      </x:c>
+      <x:c r="P112" s="19" t="str">
+        <x:v>LOC-KNEE-R-005|LOC-KNEE-PATELLAR-TENDON</x:v>
+      </x:c>
+      <x:c r="Q112" s="19" t="str">
+        <x:v>QG-KNEE-FRONT-2|QG-PROVOKE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="170" customHeight="1">
+      <x:c r="A113" s="19" t="str">
+        <x:v>QG-ITB-1</x:v>
+      </x:c>
+      <x:c r="B113" s="19" t="str">
+        <x:v>膝外侧最明显点</x:v>
+      </x:c>
+      <x:c r="C113" s="19" t="str">
+        <x:v>最痛在膝外侧稍上方，还是关节缝或膝下的骨头突起？</x:v>
+      </x:c>
+      <x:c r="D113" s="19" t="str">
+        <x:v>是固定一点还是沿大腿外侧延伸？</x:v>
+      </x:c>
+      <x:c r="E113" s="19" t="str">
+        <x:v>分清髂胫束远端邻近与其他外侧组织。</x:v>
+      </x:c>
+      <x:c r="F113" s="19" t="str">
+        <x:v>位置和范围。</x:v>
+      </x:c>
+      <x:c r="G113" s="19" t="str">
+        <x:v>分别查看髂胫束邻近、外侧关节线及腓骨头；不凭位置判断摩擦。</x:v>
+      </x:c>
+      <x:c r="H113" s="19" t="str">
+        <x:v>LOCATION</x:v>
+      </x:c>
+      <x:c r="I113" s="19" t="str">
+        <x:v>KNEE</x:v>
+      </x:c>
+      <x:c r="J113" s="19"/>
+      <x:c r="K113" s="19" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L113" s="19" t="str">
+        <x:v>Display_Only</x:v>
+      </x:c>
+      <x:c r="M113" s="19" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="N113" s="19" t="str">
+        <x:v>baseline://clinical-extension/ConsultationGuide/QG-KNEE-LATERAL-1
+book://magee-local#pdf=739&amp;print=730</x:v>
+      </x:c>
+      <x:c r="O113" s="19" t="str">
+        <x:v>2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
+      </x:c>
+      <x:c r="P113" s="19" t="str">
+        <x:v>LOC-KNEE-R-012</x:v>
+      </x:c>
+      <x:c r="Q113" s="19" t="str">
+        <x:v>QG-KNEE-LATERAL-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="170" customHeight="1">
+      <x:c r="A114" s="19" t="str">
+        <x:v>QG-ITB-2</x:v>
+      </x:c>
+      <x:c r="B114" s="19" t="str">
+        <x:v>跑步与重复屈伸</x:v>
+      </x:c>
+      <x:c r="C114" s="19" t="str">
+        <x:v>跑步或骑车到什么时间、距离后出现？下坡有不同吗？</x:v>
+      </x:c>
+      <x:c r="D114" s="19" t="str">
+        <x:v>停下后多久缓解？近期跑量、坡度或骑车设置是否改变？</x:v>
+      </x:c>
+      <x:c r="E114" s="19" t="str">
+        <x:v>明确重复屈伸和负荷背景。</x:v>
+      </x:c>
+      <x:c r="F114" s="19" t="str">
+        <x:v>出现阈值、恢复时间及活动变化。</x:v>
+      </x:c>
+      <x:c r="G114" s="19" t="str">
+        <x:v>选择可耐受的重复任务观察髋膝控制和症状变化；特殊诱发试验仅作补充。</x:v>
+      </x:c>
+      <x:c r="H114" s="19" t="str">
+        <x:v>LOCATION</x:v>
+      </x:c>
+      <x:c r="I114" s="19" t="str">
+        <x:v>KNEE</x:v>
+      </x:c>
+      <x:c r="J114" s="19"/>
+      <x:c r="K114" s="19" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="L114" s="19" t="str">
+        <x:v>Display_Only</x:v>
+      </x:c>
+      <x:c r="M114" s="19" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="N114" s="19" t="str">
+        <x:v>baseline://clinical-extension/ConsultationGuide/QG-KNEE-LATERAL-2
+book://magee-local#pdf=739&amp;print=730</x:v>
+      </x:c>
+      <x:c r="O114" s="19" t="str">
+        <x:v>2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
+      </x:c>
+      <x:c r="P114" s="19" t="str">
+        <x:v>LOC-KNEE-R-012</x:v>
+      </x:c>
+      <x:c r="Q114" s="19" t="str">
+        <x:v>QG-KNEE-LATERAL-2|QG-PROVOKE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="170" customHeight="1">
+      <x:c r="A115" s="19" t="str">
+        <x:v>QG-FIBHEAD-1</x:v>
+      </x:c>
+      <x:c r="B115" s="19" t="str">
+        <x:v>腓骨头周围的位置</x:v>
+      </x:c>
+      <x:c r="C115" s="19" t="str">
+        <x:v>膝下外侧突起附近痛，还是沿小腿、足背有麻或电击感？</x:v>
+      </x:c>
+      <x:c r="D115" s="19" t="str">
+        <x:v>是否跷腿、蹲久或护具压到后出现？</x:v>
+      </x:c>
+      <x:c r="E115" s="19" t="str">
+        <x:v>区分局部接触与感觉分布。</x:v>
+      </x:c>
+      <x:c r="F115" s="19" t="str">
+        <x:v>骨突、肌腱邻近或远端感觉表现。</x:v>
+      </x:c>
+      <x:c r="G115" s="19" t="str">
+        <x:v>结合股二头肌腱、近端胫腓关节及腓总神经筛查。</x:v>
+      </x:c>
+      <x:c r="H115" s="19" t="str">
+        <x:v>LOCATION</x:v>
+      </x:c>
+      <x:c r="I115" s="19" t="str">
+        <x:v>KNEE</x:v>
+      </x:c>
+      <x:c r="J115" s="19"/>
+      <x:c r="K115" s="19" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L115" s="19" t="str">
+        <x:v>Display_Only</x:v>
+      </x:c>
+      <x:c r="M115" s="19" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="N115" s="19" t="str">
+        <x:v>baseline://clinical-extension/ConsultationGuide/QG-KNEE-LATERAL-1
+book://magee-local#pdf=739&amp;print=730</x:v>
+      </x:c>
+      <x:c r="O115" s="19" t="str">
+        <x:v>2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
+      </x:c>
+      <x:c r="P115" s="19" t="str">
+        <x:v>LOC-KNEE-R-011</x:v>
+      </x:c>
+      <x:c r="Q115" s="19" t="str">
+        <x:v>QG-KNEE-LATERAL-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="170" customHeight="1">
+      <x:c r="A116" s="19" t="str">
+        <x:v>QG-FIBHEAD-2</x:v>
+      </x:c>
+      <x:c r="B116" s="19" t="str">
+        <x:v>动作与力量变化</x:v>
+      </x:c>
+      <x:c r="C116" s="19" t="str">
+        <x:v>弯膝发力、转身或蹲下时会不会疼？</x:v>
+      </x:c>
+      <x:c r="D116" s="19" t="str">
+        <x:v>有没有新出现抬脚、伸趾或向外转脚无力？</x:v>
+      </x:c>
+      <x:c r="E116" s="19" t="str">
+        <x:v>了解局部受力与远端运动变化。</x:v>
+      </x:c>
+      <x:c r="F116" s="19" t="str">
+        <x:v>诱发动作及是否有新发无力。</x:v>
+      </x:c>
+      <x:c r="G116" s="19" t="str">
+        <x:v>新发明显远端无力应及时医学评估；无此表现时再对照局部检查。</x:v>
+      </x:c>
+      <x:c r="H116" s="19" t="str">
+        <x:v>LOCATION</x:v>
+      </x:c>
+      <x:c r="I116" s="19" t="str">
+        <x:v>KNEE</x:v>
+      </x:c>
+      <x:c r="J116" s="19"/>
+      <x:c r="K116" s="19" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="L116" s="19" t="str">
+        <x:v>Display_Only</x:v>
+      </x:c>
+      <x:c r="M116" s="19" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="N116" s="19" t="str">
+        <x:v>baseline://clinical-extension/ConsultationGuide/QG-KNEE-LATERAL-2
+book://magee-local#pdf=739&amp;print=730</x:v>
+      </x:c>
+      <x:c r="O116" s="19" t="str">
+        <x:v>2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
+      </x:c>
+      <x:c r="P116" s="19" t="str">
+        <x:v>LOC-KNEE-R-011</x:v>
+      </x:c>
+      <x:c r="Q116" s="19" t="str">
+        <x:v>QG-KNEE-LATERAL-2|QG-PROVOKE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="170" customHeight="1">
+      <x:c r="A117" s="19" t="str">
+        <x:v>QG-TOE-H-1</x:v>
+      </x:c>
+      <x:c r="B117" s="19" t="str">
+        <x:v>足趾不适的位置</x:v>
+      </x:c>
+      <x:c r="C117" s="19" t="str">
+        <x:v>大脚趾最痛在根部、趾间关节、趾尖还是趾甲旁？</x:v>
+      </x:c>
+      <x:c r="D117" s="19" t="str">
+        <x:v>有无鞋挤压、皮肤破损或麻刺？</x:v>
+      </x:c>
+      <x:c r="E117" s="19" t="str">
+        <x:v>防止把所有足趾问题都归入跖趾关节。</x:v>
+      </x:c>
+      <x:c r="F117" s="19" t="str">
+        <x:v>具体趾与关节、皮肤或趾间分布。</x:v>
+      </x:c>
+      <x:c r="G117" s="19" t="str">
+        <x:v>按部位选择关节活动、屈伸肌腱和感觉检查；皮肤及甲周问题需相应专业处理。</x:v>
+      </x:c>
+      <x:c r="H117" s="19" t="str">
+        <x:v>LOCATION</x:v>
+      </x:c>
+      <x:c r="I117" s="19" t="str">
+        <x:v>ANKLE_FOOT</x:v>
+      </x:c>
+      <x:c r="J117" s="19"/>
+      <x:c r="K117" s="19" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L117" s="19" t="str">
+        <x:v>Display_Only</x:v>
+      </x:c>
+      <x:c r="M117" s="19" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="N117" s="19" t="str">
+        <x:v>baseline://clinical-extension/ConsultationGuide/QG-AF-R-012-1
+book://magee-local#pdf=857&amp;print=848</x:v>
+      </x:c>
+      <x:c r="O117" s="19" t="str">
+        <x:v>2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
+      </x:c>
+      <x:c r="P117" s="19" t="str">
+        <x:v>LOC-TOE-HALLUX</x:v>
+      </x:c>
+      <x:c r="Q117" s="19" t="str">
+        <x:v>QG-AF-R-012-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="170" customHeight="1">
+      <x:c r="A118" s="19" t="str">
+        <x:v>QG-TOE-H-2</x:v>
+      </x:c>
+      <x:c r="B118" s="19" t="str">
+        <x:v>鞋内与蹬地反应</x:v>
+      </x:c>
+      <x:c r="C118" s="19" t="str">
+        <x:v>穿鞋、赤脚、弯伸脚趾和走路蹬地时有什么区别？</x:v>
+      </x:c>
+      <x:c r="D118" s="19" t="str">
+        <x:v>换宽一些的鞋或减少走路后是否改变？</x:v>
+      </x:c>
+      <x:c r="E118" s="19" t="str">
+        <x:v>比较挤压、运动及负重。</x:v>
+      </x:c>
+      <x:c r="F118" s="19" t="str">
+        <x:v>接触与动作相关性。</x:v>
+      </x:c>
+      <x:c r="G118" s="19" t="str">
+        <x:v>核对鞋内空间、足趾活动及支撑，避免只查看前足跖骨头。</x:v>
+      </x:c>
+      <x:c r="H118" s="19" t="str">
+        <x:v>LOCATION</x:v>
+      </x:c>
+      <x:c r="I118" s="19" t="str">
+        <x:v>ANKLE_FOOT</x:v>
+      </x:c>
+      <x:c r="J118" s="19"/>
+      <x:c r="K118" s="19" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="L118" s="19" t="str">
+        <x:v>Display_Only</x:v>
+      </x:c>
+      <x:c r="M118" s="19" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="N118" s="19" t="str">
+        <x:v>baseline://clinical-extension/ConsultationGuide/QG-AF-R-012-2
+book://magee-local#pdf=857&amp;print=848</x:v>
+      </x:c>
+      <x:c r="O118" s="19" t="str">
+        <x:v>2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
+      </x:c>
+      <x:c r="P118" s="19" t="str">
+        <x:v>LOC-TOE-HALLUX</x:v>
+      </x:c>
+      <x:c r="Q118" s="19" t="str">
+        <x:v>QG-AF-R-012-2|QG-PROVOKE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="170" customHeight="1">
+      <x:c r="A119" s="19" t="str">
+        <x:v>QG-TOE-H-3</x:v>
+      </x:c>
+      <x:c r="B119" s="19" t="str">
+        <x:v>受伤与外形变化</x:v>
+      </x:c>
+      <x:c r="C119" s="19" t="str">
+        <x:v>有没有踢撞、被踩或脚趾被掰到？</x:v>
+      </x:c>
+      <x:c r="D119" s="19" t="str">
+        <x:v>是否出现变形、明显肿胀、瘀斑、伤口或突然红热？</x:v>
+      </x:c>
+      <x:c r="E119" s="19" t="str">
+        <x:v>了解急性损伤及局部异常。</x:v>
+      </x:c>
+      <x:c r="F119" s="19" t="str">
+        <x:v>受伤机制与结构、皮肤变化。</x:v>
+      </x:c>
+      <x:c r="G119" s="19" t="str">
+        <x:v>明显变形、开放伤或急性红肿热优先医学评估，不强行活动矫正。</x:v>
+      </x:c>
+      <x:c r="H119" s="19" t="str">
+        <x:v>LOCATION</x:v>
+      </x:c>
+      <x:c r="I119" s="19" t="str">
+        <x:v>ANKLE_FOOT</x:v>
+      </x:c>
+      <x:c r="J119" s="19"/>
+      <x:c r="K119" s="19" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L119" s="19" t="str">
+        <x:v>Display_Only</x:v>
+      </x:c>
+      <x:c r="M119" s="19" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="N119" s="19" t="str">
+        <x:v>baseline://clinical-extension/ConsultationGuide/QG-AF-R-012-3
+book://magee-local#pdf=857&amp;print=848</x:v>
+      </x:c>
+      <x:c r="O119" s="19" t="str">
+        <x:v>2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
+      </x:c>
+      <x:c r="P119" s="19" t="str">
+        <x:v>LOC-TOE-HALLUX</x:v>
+      </x:c>
+      <x:c r="Q119" s="19" t="str">
+        <x:v>QG-AF-R-012-3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="170" customHeight="1">
+      <x:c r="A120" s="19" t="str">
+        <x:v>QG-TOE-L-1</x:v>
+      </x:c>
+      <x:c r="B120" s="19" t="str">
+        <x:v>足趾不适的位置</x:v>
+      </x:c>
+      <x:c r="C120" s="19" t="str">
+        <x:v>哪根脚趾、哪个位置最不舒服？根部、关节、趾尖还是趾间？</x:v>
+      </x:c>
+      <x:c r="D120" s="19" t="str">
+        <x:v>有无鞋挤压、皮肤破损或麻刺？</x:v>
+      </x:c>
+      <x:c r="E120" s="19" t="str">
+        <x:v>防止把所有足趾问题都归入跖趾关节。</x:v>
+      </x:c>
+      <x:c r="F120" s="19" t="str">
+        <x:v>具体趾与关节、皮肤或趾间分布。</x:v>
+      </x:c>
+      <x:c r="G120" s="19" t="str">
+        <x:v>按部位选择关节活动、屈伸肌腱和感觉检查；皮肤及甲周问题需相应专业处理。</x:v>
+      </x:c>
+      <x:c r="H120" s="19" t="str">
+        <x:v>LOCATION</x:v>
+      </x:c>
+      <x:c r="I120" s="19" t="str">
+        <x:v>ANKLE_FOOT</x:v>
+      </x:c>
+      <x:c r="J120" s="19"/>
+      <x:c r="K120" s="19" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L120" s="19" t="str">
+        <x:v>Display_Only</x:v>
+      </x:c>
+      <x:c r="M120" s="19" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="N120" s="19" t="str">
+        <x:v>baseline://clinical-extension/ConsultationGuide/QG-AF-R-011-1
+book://magee-local#pdf=857&amp;print=848</x:v>
+      </x:c>
+      <x:c r="O120" s="19" t="str">
+        <x:v>2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
+      </x:c>
+      <x:c r="P120" s="19" t="str">
+        <x:v>LOC-TOE-LESSER</x:v>
+      </x:c>
+      <x:c r="Q120" s="19" t="str">
+        <x:v>QG-AF-R-011-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="170" customHeight="1">
+      <x:c r="A121" s="19" t="str">
+        <x:v>QG-TOE-L-2</x:v>
+      </x:c>
+      <x:c r="B121" s="19" t="str">
+        <x:v>鞋内与蹬地反应</x:v>
+      </x:c>
+      <x:c r="C121" s="19" t="str">
+        <x:v>穿鞋、赤脚、弯伸脚趾和走路蹬地时有什么区别？</x:v>
+      </x:c>
+      <x:c r="D121" s="19" t="str">
+        <x:v>换宽一些的鞋或减少走路后是否改变？</x:v>
+      </x:c>
+      <x:c r="E121" s="19" t="str">
+        <x:v>比较挤压、运动及负重。</x:v>
+      </x:c>
+      <x:c r="F121" s="19" t="str">
+        <x:v>接触与动作相关性。</x:v>
+      </x:c>
+      <x:c r="G121" s="19" t="str">
+        <x:v>核对鞋内空间、足趾活动及支撑，避免只查看前足跖骨头。</x:v>
+      </x:c>
+      <x:c r="H121" s="19" t="str">
+        <x:v>LOCATION</x:v>
+      </x:c>
+      <x:c r="I121" s="19" t="str">
+        <x:v>ANKLE_FOOT</x:v>
+      </x:c>
+      <x:c r="J121" s="19"/>
+      <x:c r="K121" s="19" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="L121" s="19" t="str">
+        <x:v>Display_Only</x:v>
+      </x:c>
+      <x:c r="M121" s="19" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="N121" s="19" t="str">
+        <x:v>baseline://clinical-extension/ConsultationGuide/QG-AF-R-011-2
+book://magee-local#pdf=857&amp;print=848</x:v>
+      </x:c>
+      <x:c r="O121" s="19" t="str">
+        <x:v>2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
+      </x:c>
+      <x:c r="P121" s="19" t="str">
+        <x:v>LOC-TOE-LESSER</x:v>
+      </x:c>
+      <x:c r="Q121" s="19" t="str">
+        <x:v>QG-AF-R-011-2|QG-PROVOKE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="170" customHeight="1">
+      <x:c r="A122" s="19" t="str">
+        <x:v>QG-TOE-L-3</x:v>
+      </x:c>
+      <x:c r="B122" s="19" t="str">
+        <x:v>受伤与外形变化</x:v>
+      </x:c>
+      <x:c r="C122" s="19" t="str">
+        <x:v>有没有踢撞、被踩或脚趾被掰到？</x:v>
+      </x:c>
+      <x:c r="D122" s="19" t="str">
+        <x:v>是否出现变形、明显肿胀、瘀斑、伤口或突然红热？</x:v>
+      </x:c>
+      <x:c r="E122" s="19" t="str">
+        <x:v>了解急性损伤及局部异常。</x:v>
+      </x:c>
+      <x:c r="F122" s="19" t="str">
+        <x:v>受伤机制与结构、皮肤变化。</x:v>
+      </x:c>
+      <x:c r="G122" s="19" t="str">
+        <x:v>明显变形、开放伤或急性红肿热优先医学评估，不强行活动矫正。</x:v>
+      </x:c>
+      <x:c r="H122" s="19" t="str">
+        <x:v>LOCATION</x:v>
+      </x:c>
+      <x:c r="I122" s="19" t="str">
+        <x:v>ANKLE_FOOT</x:v>
+      </x:c>
+      <x:c r="J122" s="19"/>
+      <x:c r="K122" s="19" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L122" s="19" t="str">
+        <x:v>Display_Only</x:v>
+      </x:c>
+      <x:c r="M122" s="19" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="N122" s="19" t="str">
+        <x:v>baseline://clinical-extension/ConsultationGuide/QG-AF-R-011-3
+book://magee-local#pdf=857&amp;print=848</x:v>
+      </x:c>
+      <x:c r="O122" s="19" t="str">
+        <x:v>2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
+      </x:c>
+      <x:c r="P122" s="19" t="str">
+        <x:v>LOC-TOE-LESSER</x:v>
+      </x:c>
+      <x:c r="Q122" s="19" t="str">
+        <x:v>QG-AF-R-011-3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="170" customHeight="1">
+      <x:c r="A123" s="19" t="str">
+        <x:v>QG-LM-LOCATION-REGION</x:v>
+      </x:c>
+      <x:c r="B123" s="19" t="str">
+        <x:v>骨缘还是后侧软组织</x:v>
+      </x:c>
+      <x:c r="C123" s="19" t="str">
+        <x:v>小腿内侧最不舒服的位置在哪里？靠近硬的骨边，还是更后面的软组织？</x:v>
+      </x:c>
+      <x:c r="D123" s="19" t="str">
+        <x:v>是一个点还是沿着一段？偏上段、中段还是下段？</x:v>
+      </x:c>
+      <x:c r="E123" s="19" t="str">
+        <x:v>了解骨缘和邻近软组织的不适分布。</x:v>
+      </x:c>
+      <x:c r="F123" s="19" t="str">
+        <x:v>疼痛范围、局灶或分段分布，以及与骨缘的关系。</x:v>
+      </x:c>
+      <x:c r="G123" s="19" t="str">
+        <x:v>分别查看胫骨内侧缘压痛和邻近肌群，局灶骨性压痛可补充骨应力相关评估。</x:v>
+      </x:c>
+      <x:c r="H123" s="19" t="str">
+        <x:v>REGION</x:v>
+      </x:c>
+      <x:c r="I123" s="19" t="str">
+        <x:v>LOWER_LEG</x:v>
+      </x:c>
+      <x:c r="J123" s="19" t="str">
+        <x:v>LL-R-003</x:v>
+      </x:c>
+      <x:c r="K123" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L123" s="19" t="str">
+        <x:v>Display_Only</x:v>
+      </x:c>
+      <x:c r="M123" s="19" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="N123" s="19" t="str">
+        <x:v>本批部位问诊为编辑稿，待临床审核；基础检查来自主库 Lower Leg Remaining L3 Review v2.6、Core Assessment Protocol Refinement v3.2。参考 https://www.orthoinfo.org/diseases--conditions/shin-splints/ 及 https://www.orthoinfo.org/diseases--conditions/posterior-tibial-tendon-dysfunction/ ，只支持问诊和评估背景，不支持由位置诊断或自动处理。</x:v>
+      </x:c>
+      <x:c r="O123" s="19" t="str">
+        <x:v>2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
+      </x:c>
+      <x:c r="P123" s="19"/>
+      <x:c r="Q123" s="19"/>
+    </x:row>
+    <x:row r="124" ht="170" customHeight="1">
+      <x:c r="A124" s="19" t="str">
+        <x:v>QG-LM-ACTIVITY-REGION</x:v>
+      </x:c>
+      <x:c r="B124" s="19" t="str">
+        <x:v>负重和跑跳时的表现</x:v>
+      </x:c>
+      <x:c r="C124" s="19" t="str">
+        <x:v>走路、跑步或跳跃时会不会出现不适？</x:v>
+      </x:c>
+      <x:c r="D124" s="19" t="str">
+        <x:v>开始活动就出现，活动一段时间后出现，还是活动后仍持续？休息时如何？</x:v>
+      </x:c>
+      <x:c r="E124" s="19" t="str">
+        <x:v>了解骨缘不适与重复负重及活动时机的关系。</x:v>
+      </x:c>
+      <x:c r="F124" s="19" t="str">
+        <x:v>诱发活动、出现时机、活动后和休息时的变化。</x:v>
+      </x:c>
+      <x:c r="G124" s="19" t="str">
+        <x:v>补充骨缘局部检查和活动耐受背景；不根据一种活动直接归因。</x:v>
+      </x:c>
+      <x:c r="H124" s="19" t="str">
+        <x:v>REGION</x:v>
+      </x:c>
+      <x:c r="I124" s="19" t="str">
+        <x:v>LOWER_LEG</x:v>
+      </x:c>
+      <x:c r="J124" s="19" t="str">
+        <x:v>LL-R-003</x:v>
+      </x:c>
+      <x:c r="K124" s="19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L124" s="19" t="str">
+        <x:v>Display_Only</x:v>
+      </x:c>
+      <x:c r="M124" s="19" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="N124" s="19" t="str">
+        <x:v>本批部位问诊为编辑稿，待临床审核；基础检查来自主库 Lower Leg Remaining L3 Review v2.6、Core Assessment Protocol Refinement v3.2。参考 https://www.orthoinfo.org/diseases--conditions/shin-splints/ 及 https://www.orthoinfo.org/diseases--conditions/posterior-tibial-tendon-dysfunction/ ，只支持问诊和评估背景，不支持由位置诊断或自动处理。</x:v>
+      </x:c>
+      <x:c r="O124" s="19" t="str">
+        <x:v>2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
+      </x:c>
+      <x:c r="P124" s="19"/>
+      <x:c r="Q124" s="19" t="str">
+        <x:v>QG-PROVOKE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" ht="170" customHeight="1">
+      <x:c r="A125" s="19" t="str">
+        <x:v>QG-LM-CHANGE-REGION</x:v>
+      </x:c>
+      <x:c r="B125" s="19" t="str">
+        <x:v>近期训练变化</x:v>
+      </x:c>
+      <x:c r="C125" s="19" t="str">
+        <x:v>近期跑量、速度、坡度、场地或鞋子有没有变化？</x:v>
+      </x:c>
+      <x:c r="D125" s="19" t="str">
+        <x:v>是否增加连续训练天数，或在休息后重新开始训练？</x:v>
+      </x:c>
+      <x:c r="E125" s="19" t="str">
+        <x:v>了解近期负重活动的变化。</x:v>
+      </x:c>
+      <x:c r="F125" s="19" t="str">
+        <x:v>训练强度、频率、时长、场地及鞋子的变化。</x:v>
+      </x:c>
+      <x:c r="G125" s="19" t="str">
+        <x:v>为负重耐受、踝背屈及相关肌力评估提供活动背景。</x:v>
+      </x:c>
+      <x:c r="H125" s="19" t="str">
+        <x:v>REGION</x:v>
+      </x:c>
+      <x:c r="I125" s="19" t="str">
+        <x:v>LOWER_LEG</x:v>
+      </x:c>
+      <x:c r="J125" s="19" t="str">
+        <x:v>LL-R-003</x:v>
+      </x:c>
+      <x:c r="K125" s="19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L125" s="19" t="str">
+        <x:v>Display_Only</x:v>
+      </x:c>
+      <x:c r="M125" s="19" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="N125" s="19" t="str">
+        <x:v>本批部位问诊为编辑稿，待临床审核；基础检查来自主库 Lower Leg Remaining L3 Review v2.6、Core Assessment Protocol Refinement v3.2。参考 https://www.orthoinfo.org/diseases--conditions/shin-splints/ 及 https://www.orthoinfo.org/diseases--conditions/posterior-tibial-tendon-dysfunction/ ，只支持问诊和评估背景，不支持由位置诊断或自动处理。</x:v>
+      </x:c>
+      <x:c r="O125" s="19" t="str">
+        <x:v>2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
+      </x:c>
+      <x:c r="P125" s="19"/>
+      <x:c r="Q125" s="19"/>
+    </x:row>
+    <x:row r="126" ht="170" customHeight="1">
+      <x:c r="A126" s="19" t="str">
+        <x:v>QG-LM-ASSOCIATED-REGION</x:v>
+      </x:c>
+      <x:c r="B126" s="19" t="str">
+        <x:v>其他伴随表现</x:v>
+      </x:c>
+      <x:c r="C126" s="19" t="str">
+        <x:v>有没有局部肿胀、麻木、灼热或明显无力？</x:v>
+      </x:c>
+      <x:c r="D126" s="19" t="str">
+        <x:v>是否每次到相似时间或距离就出现？停止活动后多久缓解？</x:v>
+      </x:c>
+      <x:c r="E126" s="19" t="str">
+        <x:v>了解骨缘疼痛之外的感觉、力量及运动后变化。</x:v>
+      </x:c>
+      <x:c r="F126" s="19" t="str">
+        <x:v>感觉分布、伴随肿胀和无力，以及可重复的出现时机。</x:v>
+      </x:c>
+      <x:c r="G126" s="19" t="str">
+        <x:v>为神经筛查或运动诱发症状的进一步评估提供方向。</x:v>
+      </x:c>
+      <x:c r="H126" s="19" t="str">
+        <x:v>REGION</x:v>
+      </x:c>
+      <x:c r="I126" s="19" t="str">
+        <x:v>LOWER_LEG</x:v>
+      </x:c>
+      <x:c r="J126" s="19" t="str">
+        <x:v>LL-R-003</x:v>
+      </x:c>
+      <x:c r="K126" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="L126" s="19" t="str">
+        <x:v>Display_Only</x:v>
+      </x:c>
+      <x:c r="M126" s="19" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="N126" s="19" t="str">
+        <x:v>本批部位问诊为编辑稿，待临床审核；基础检查来自主库 Lower Leg Remaining L3 Review v2.6、Core Assessment Protocol Refinement v3.2。参考 https://www.orthoinfo.org/diseases--conditions/shin-splints/ 及 https://www.orthoinfo.org/diseases--conditions/posterior-tibial-tendon-dysfunction/ ，只支持问诊和评估背景，不支持由位置诊断或自动处理。</x:v>
+      </x:c>
+      <x:c r="O126" s="19" t="str">
+        <x:v>2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
+      </x:c>
+      <x:c r="P126" s="19"/>
+      <x:c r="Q126" s="19"/>
+    </x:row>
+    <x:row r="127" ht="170" customHeight="1">
+      <x:c r="A127" s="19" t="str">
+        <x:v>QG-LPM-LOCATION-REGION</x:v>
+      </x:c>
+      <x:c r="B127" s="19" t="str">
+        <x:v>不适的具体范围</x:v>
+      </x:c>
+      <x:c r="C127" s="19" t="str">
+        <x:v>不适在小腿内侧哪一段？有没有延伸到内踝、足弓或足趾？</x:v>
+      </x:c>
+      <x:c r="D127" s="19" t="str">
+        <x:v>更靠近骨缘，还是后侧肌腹？浅表按压和活动时的位置是否相同？</x:v>
+      </x:c>
+      <x:c r="E127" s="19" t="str">
+        <x:v>了解小腿后内侧与内踝、足部之间的不适分布。</x:v>
+      </x:c>
+      <x:c r="F127" s="19" t="str">
+        <x:v>高度、骨缘或软组织位置，以及向远端延伸的范围。</x:v>
+      </x:c>
+      <x:c r="G127" s="19" t="str">
+        <x:v>为腓肠肌内侧头、比目鱼肌、胫骨后肌及长屈肌群的检查提供定位背景。</x:v>
+      </x:c>
+      <x:c r="H127" s="19" t="str">
+        <x:v>REGION</x:v>
+      </x:c>
+      <x:c r="I127" s="19" t="str">
+        <x:v>LOWER_LEG</x:v>
+      </x:c>
+      <x:c r="J127" s="19" t="str">
+        <x:v>LL-R-007</x:v>
+      </x:c>
+      <x:c r="K127" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L127" s="19" t="str">
+        <x:v>Display_Only</x:v>
+      </x:c>
+      <x:c r="M127" s="19" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="N127" s="19" t="str">
+        <x:v>本批部位问诊为编辑稿，待临床审核；基础检查来自主库 Lower Leg Remaining L3 Review v2.6、Core Assessment Protocol Refinement v3.2。参考 https://www.orthoinfo.org/diseases--conditions/shin-splints/ 及 https://www.orthoinfo.org/diseases--conditions/posterior-tibial-tendon-dysfunction/ ，只支持问诊和评估背景，不支持由位置诊断或自动处理。</x:v>
+      </x:c>
+      <x:c r="O127" s="19" t="str">
+        <x:v>2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
+      </x:c>
+      <x:c r="P127" s="19"/>
+      <x:c r="Q127" s="19"/>
+    </x:row>
+    <x:row r="128" ht="170" customHeight="1">
+      <x:c r="A128" s="19" t="str">
+        <x:v>QG-LPM-ACTIVITY-REGION</x:v>
+      </x:c>
+      <x:c r="B128" s="19" t="str">
+        <x:v>哪些动作不舒服</x:v>
+      </x:c>
+      <x:c r="C128" s="19" t="str">
+        <x:v>走路蹬地、提踵、脚向内转或屈脚趾时，哪些动作会不舒服？</x:v>
+      </x:c>
+      <x:c r="D128" s="19" t="str">
+        <x:v>拉长时和发力时是否不同？膝盖伸直或弯曲时有什么变化？</x:v>
+      </x:c>
+      <x:c r="E128" s="19" t="str">
+        <x:v>了解不适与跖屈、内翻和屈趾发力，以及小腿后侧拉长的关系。</x:v>
+      </x:c>
+      <x:c r="F128" s="19" t="str">
+        <x:v>诱发动作、拉长与发力差异，以及膝位变化。</x:v>
+      </x:c>
+      <x:c r="G128" s="19" t="str">
+        <x:v>可分别查看伸膝位和屈膝位背屈、提踵、内翻抗阻及屈趾表现。</x:v>
+      </x:c>
+      <x:c r="H128" s="19" t="str">
+        <x:v>REGION</x:v>
+      </x:c>
+      <x:c r="I128" s="19" t="str">
+        <x:v>LOWER_LEG</x:v>
+      </x:c>
+      <x:c r="J128" s="19" t="str">
+        <x:v>LL-R-007</x:v>
+      </x:c>
+      <x:c r="K128" s="19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L128" s="19" t="str">
+        <x:v>Display_Only</x:v>
+      </x:c>
+      <x:c r="M128" s="19" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="N128" s="19" t="str">
+        <x:v>本批部位问诊为编辑稿，待临床审核；基础检查来自主库 Lower Leg Remaining L3 Review v2.6、Core Assessment Protocol Refinement v3.2。参考 https://www.orthoinfo.org/diseases--conditions/shin-splints/ 及 https://www.orthoinfo.org/diseases--conditions/posterior-tibial-tendon-dysfunction/ ，只支持问诊和评估背景，不支持由位置诊断或自动处理。</x:v>
+      </x:c>
+      <x:c r="O128" s="19" t="str">
+        <x:v>2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
+      </x:c>
+      <x:c r="P128" s="19"/>
+      <x:c r="Q128" s="19" t="str">
+        <x:v>QG-PROVOKE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" ht="170" customHeight="1">
+      <x:c r="A129" s="19" t="str">
+        <x:v>QG-LPM-CHANGE-REGION</x:v>
+      </x:c>
+      <x:c r="B129" s="19" t="str">
+        <x:v>近期活动变化</x:v>
+      </x:c>
+      <x:c r="C129" s="19" t="str">
+        <x:v>近期走路、跑跳、上坡或提踵训练的量有没有变化？</x:v>
+      </x:c>
+      <x:c r="D129" s="19" t="str">
+        <x:v>是否有一次明显牵拉、蹬地，或连续多天高强度活动？</x:v>
+      </x:c>
+      <x:c r="E129" s="19" t="str">
+        <x:v>了解后侧肌群拉长和发力的活动背景。</x:v>
+      </x:c>
+      <x:c r="F129" s="19" t="str">
+        <x:v>突然出现还是逐渐出现，以及活动强度、频率与时长变化。</x:v>
+      </x:c>
+      <x:c r="G129" s="19" t="str">
+        <x:v>为局部组织状态、跖屈和内翻力量及活动表现的查看提供背景。</x:v>
+      </x:c>
+      <x:c r="H129" s="19" t="str">
+        <x:v>REGION</x:v>
+      </x:c>
+      <x:c r="I129" s="19" t="str">
+        <x:v>LOWER_LEG</x:v>
+      </x:c>
+      <x:c r="J129" s="19" t="str">
+        <x:v>LL-R-007</x:v>
+      </x:c>
+      <x:c r="K129" s="19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L129" s="19" t="str">
+        <x:v>Display_Only</x:v>
+      </x:c>
+      <x:c r="M129" s="19" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="N129" s="19" t="str">
+        <x:v>本批部位问诊为编辑稿，待临床审核；基础检查来自主库 Lower Leg Remaining L3 Review v2.6、Core Assessment Protocol Refinement v3.2。参考 https://www.orthoinfo.org/diseases--conditions/shin-splints/ 及 https://www.orthoinfo.org/diseases--conditions/posterior-tibial-tendon-dysfunction/ ，只支持问诊和评估背景，不支持由位置诊断或自动处理。</x:v>
+      </x:c>
+      <x:c r="O129" s="19" t="str">
+        <x:v>2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
+      </x:c>
+      <x:c r="P129" s="19"/>
+      <x:c r="Q129" s="19"/>
+    </x:row>
+    <x:row r="130" ht="170" customHeight="1">
+      <x:c r="A130" s="19" t="str">
+        <x:v>QG-LPM-ASSOCIATED-REGION</x:v>
+      </x:c>
+      <x:c r="B130" s="19" t="str">
+        <x:v>感觉和肿胀变化</x:v>
+      </x:c>
+      <x:c r="C130" s="19" t="str">
+        <x:v>有没有麻木、向足部放射的不适，或明显肿胀？</x:v>
+      </x:c>
+      <x:c r="D130" s="19" t="str">
+        <x:v>感觉在哪些位置？肿胀是否突然出现或加重？</x:v>
+      </x:c>
+      <x:c r="E130" s="19" t="str">
+        <x:v>了解肌肉拉长、发力以外的伴随表现。</x:v>
+      </x:c>
+      <x:c r="F130" s="19" t="str">
+        <x:v>感觉分布、肿胀范围与变化经过。</x:v>
+      </x:c>
+      <x:c r="G130" s="19" t="str">
+        <x:v>感觉异常需结合分布补充神经筛查；新发单侧明显肿胀、发热或变色，应先安排医学评估，不以肌肉紧张解释。</x:v>
+      </x:c>
+      <x:c r="H130" s="19" t="str">
+        <x:v>REGION</x:v>
+      </x:c>
+      <x:c r="I130" s="19" t="str">
+        <x:v>LOWER_LEG</x:v>
+      </x:c>
+      <x:c r="J130" s="19" t="str">
+        <x:v>LL-R-007</x:v>
+      </x:c>
+      <x:c r="K130" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="L130" s="19" t="str">
+        <x:v>Display_Only</x:v>
+      </x:c>
+      <x:c r="M130" s="19" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="N130" s="19" t="str">
+        <x:v>本批部位问诊为编辑稿，待临床审核；基础检查来自主库 Lower Leg Remaining L3 Review v2.6、Core Assessment Protocol Refinement v3.2。参考 https://www.orthoinfo.org/diseases--conditions/shin-splints/ 及 https://www.orthoinfo.org/diseases--conditions/posterior-tibial-tendon-dysfunction/ ，只支持问诊和评估背景，不支持由位置诊断或自动处理。</x:v>
+      </x:c>
+      <x:c r="O130" s="19" t="str">
+        <x:v>2026-10-03：完成教学文案与关联的辅助审核；仍需专业人员结合实际检查判断。问诊仅供教学，不收集答案、不自动归因。</x:v>
+      </x:c>
+      <x:c r="P130" s="19"/>
+      <x:c r="Q130" s="19"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23887,10 +25478,10 @@
 骨与周围组织：胫骨后内侧；邻近筋膜</x:v>
       </x:c>
       <x:c r="F4" s="9" t="str">
-        <x:v>CORE-MUS-TP|CORE-MUS-FDL|CORE-MUS-GASTROC|CORE-MUS-SOLEUS|CORE-ROM-ANK-DF|CORE-ROM-ANK-EV|CORE-CAP-INV|CORE-CAP-PF|LL-LT-007</x:v>
+        <x:v>CORE-MUS-TP|CORE-MUS-FDL|CORE-MUS-GASTROC|CORE-MUS-SOLEUS|CORE-ROM-ANK-DF|CORE-ROM-ANK-EV|CORE-CAP-INV|CORE-CAP-PF|LL-LT-007|CORE-MUS-FHL</x:v>
       </x:c>
       <x:c r="G4" s="9" t="str">
-        <x:v>CORE-MUS-FHL|CORE-CAP-HF|CORE-CAP-ARCH-TOE|LL-LT-005|LL-LT-003</x:v>
+        <x:v>CORE-CAP-HF|CORE-CAP-ARCH-TOE|LL-LT-005|LL-LT-003</x:v>
       </x:c>
       <x:c r="H4" s="9" t="str">
         <x:v>LL-SPT-001|CORE-SPT-NEURO-DISTAL|LL-PATTERN-GAIT|LL-PATTERN-PUSH|LL-PATTERN-IMPACT</x:v>
@@ -23902,7 +25493,7 @@
         <x:v>待临床审核</x:v>
       </x:c>
       <x:c r="K4" s="9" t="str">
-        <x:v>05_RegionClinicalMap/LL-R-007,LL-R-005,LL-R-006；BodyParts3D 4.0 atlas；本项目已索引的线下康复记录</x:v>
+        <x:v>05_RegionClinicalMap/LL-R-007,LL-R-005,LL-R-006；BodyParts3D 4.0 atlas；本项目已索引的线下康复记录；本批将已有拇长屈肌检查由补充项移为直接阅读项。</x:v>
       </x:c>
       <x:c r="L4" s="9" t="str">
         <x:v>皮肤点选只给出周围组织，不识别深层单块肌肉。当前入口覆盖多个高度，腓肠肌、比目鱼肌与深层肌群供康复师结合不适范围查看；不表示同时存在问题。</x:v>
@@ -23922,10 +25513,9 @@
         <x:v>LOWER_LEG</x:v>
       </x:c>
       <x:c r="E5" s="9" t="str">
-        <x:v>前侧肌群：胫骨前肌；拇长伸肌；趾长伸肌
-前外侧补充：第三腓骨肌
-骨与周围组织：胫骨前缘；腓骨；前侧筋膜
-神经与血管：腓深神经；胫前血管</x:v>
+        <x:v>肌肉：胫骨前肌；趾长伸肌；拇长伸肌；第三腓骨肌
+骨与周围组织：胫骨前缘邻近；腓骨前方；小腿前侧筋膜
+神经与血管：深腓神经；胫前血管</x:v>
       </x:c>
       <x:c r="F5" s="9" t="str">
         <x:v>CORE-MUS-TA|CORE-MUS-EHL|CORE-MUS-EDL|CORE-ROM-ANK-PF|CORE-ROM-ANK-DF|CORE-CAP-DF|LL-LT-001</x:v>
@@ -23963,9 +25553,8 @@
         <x:v>LOWER_LEG</x:v>
       </x:c>
       <x:c r="E6" s="9" t="str">
-        <x:v>骨与周围组织：胫骨前嵴；前侧骨面；邻近骨膜
-邻近前外侧肌群：胫骨前肌；趾长伸肌；拇长伸肌
-相关活动：踝背屈与跖屈</x:v>
+        <x:v>骨与周围组织：胫骨前缘；骨膜及皮下组织
+邻近肌群：胫骨前肌；前外侧趾长伸肌、拇长伸肌</x:v>
       </x:c>
       <x:c r="F6" s="9" t="str">
         <x:v>LL-LT-002|CORE-MUS-TA|CORE-ROM-ANK-PF|CORE-ROM-ANK-DF|CORE-CAP-DF</x:v>
@@ -24003,11 +25592,10 @@
         <x:v>LOWER_LEG</x:v>
       </x:c>
       <x:c r="E7" s="9" t="str">
-        <x:v>外侧肌群：腓骨长肌；腓骨短肌
-骨与周围组织：腓骨；外侧筋膜
-神经：腓浅神经；上段邻近腓总神经
-近端邻近：腓骨头；近端胫腓关节
-远端邻近：腓骨肌腱；外踝后方</x:v>
+        <x:v>肌肉：腓骨长肌；腓骨短肌
+前外侧邻近：第三腓骨肌；趾长伸肌
+骨与周围组织：腓骨；小腿外侧筋膜
+神经邻近：浅腓神经</x:v>
       </x:c>
       <x:c r="F7" s="9" t="str">
         <x:v>CORE-MUS-PL|CORE-MUS-PB|CORE-ROM-ANK-INV|CORE-ROM-ANK-EV|CORE-CAP-EV|LL-LT-004</x:v>
@@ -24045,17 +25633,16 @@
         <x:v>LOWER_LEG</x:v>
       </x:c>
       <x:c r="E8" s="9" t="str">
-        <x:v>表浅肌群：腓肠肌内侧头；腓肠肌外侧头
-深层邻近：比目鱼肌
-局部组织：腓肠肌肌腱膜；肌腱交界；筋膜
-近端邻近：腘肌；膝后关节囊；腘窝神经血管
-后外侧邻近：腓肠神经</x:v>
+        <x:v>表浅肌群：腓肠肌内侧头与外侧头
+深层邻近：比目鱼肌；跖肌
+近膝邻近：腘肌；腘绳肌远端；膝后关节囊
+骨与周围组织：胫骨、腓骨近端后方；后侧筋膜</x:v>
       </x:c>
       <x:c r="F8" s="9" t="str">
         <x:v>CORE-MUS-GASTROC|CORE-MUS-SOLEUS|CORE-ROM-ANK-DF|CORE-CAP-PF|LL-LT-005</x:v>
       </x:c>
       <x:c r="G8" s="9" t="str">
-        <x:v>CORE-MUS-TP|CORE-MUS-FDL|LL-LT-006|CORE-MUS-PLANTARIS</x:v>
+        <x:v>CORE-MUS-TP|CORE-MUS-FDL|LL-LT-006|CORE-MUS-PLANTARIS|CORE-MUS-FHL</x:v>
       </x:c>
       <x:c r="H8" s="9" t="str">
         <x:v>LL-SPT-001|CORE-SPT-NEURO-DISTAL|LL-PATTERN-GAIT|LL-PATTERN-PUSH|LL-PATTERN-IMPACT</x:v>
@@ -24087,11 +25674,9 @@
         <x:v>LOWER_LEG</x:v>
       </x:c>
       <x:c r="E9" s="9" t="str">
-        <x:v>相关肌群：比目鱼肌；腓肠肌远端
-局部组织：后侧筋膜；肌腱膜；肌腱交界
-后内侧邻近：胫骨后肌；趾长屈肌；拇长屈肌
-远端邻近：跟腱近端
-神经血管：胫神经及后侧血管；后外侧腓肠神经</x:v>
+        <x:v>肌肉与肌腱：比目鱼肌；腓肠肌远端；跟腱近端
+深层邻近：胫骨后肌；趾长屈肌；拇长屈肌
+其他组织：跖肌腱；后侧筋膜</x:v>
       </x:c>
       <x:c r="F9" s="9" t="str">
         <x:v>CORE-MUS-SOLEUS|CORE-MUS-GASTROC|CORE-ROM-ANK-DF|CORE-CAP-PF|LL-LT-006</x:v>
@@ -24129,32 +25714,32 @@
         <x:v>ANKLE_FOOT</x:v>
       </x:c>
       <x:c r="E10" s="9" t="str">
-        <x:v>骨与局部组织：跟骨底；足跟垫
-软组织：足底筋膜近端</x:v>
+        <x:v>骨与表浅组织：跟骨底部；足跟脂肪垫；皮下组织
+前内侧邻近：足底筋膜附着区</x:v>
       </x:c>
       <x:c r="F10" s="9" t="str">
-        <x:v>AF-LT-006|AF-LT-007|CORE-ROM-ANK-DF|CORE-MUS-GASTROC|CORE-MUS-SOLEUS</x:v>
+        <x:v>AF-LT-006|CORE-ROM-ANK-DF|CORE-MUS-GASTROC|CORE-MUS-SOLEUS</x:v>
       </x:c>
       <x:c r="G10" s="9" t="str">
-        <x:v>CORE-CAP-PF|AF-SPT-004|CORE-CAP-ARCH-TOE</x:v>
+        <x:v>AF-LT-007|CORE-CAP-PF|CORE-CAP-ARCH-TOE|AF-MUS-016|CORE-ROM-ANK-EV|AF-SPT-004</x:v>
       </x:c>
       <x:c r="H10" s="9" t="str">
-        <x:v>CORE-SPT-NEURO-DISTAL</x:v>
+        <x:v>CORE-ROM-ANK-INV|CORE-SPT-NEURO-DISTAL</x:v>
       </x:c>
       <x:c r="I10" s="9" t="str">
-        <x:v>MUSCLE_STATE:邻近肌群|ROM:关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
       </x:c>
       <x:c r="J10" s="9" t="str">
         <x:v>待临床审核</x:v>
       </x:c>
       <x:c r="K10" s="9" t="str">
-        <x:v>https://pmc.ncbi.nlm.nih.gov/articles/PMC5241541/
-https://www.ncbi.nlm.nih.gov/books/NBK539705/
-https://www.ncbi.nlm.nih.gov/books/NBK587361/
-https://www.ncbi.nlm.nih.gov/books/NBK545158/</x:v>
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验踝足主动活动、抗阻及附属活动章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
       </x:c>
       <x:c r="L10" s="9" t="str">
-        <x:v>现有区域的内容入口，不改变定位边界。主要清单供康复师查阅，不表示全部项目必做。</x:v>
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M10" s="20" t="b">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="210" customHeight="1">
@@ -24171,8 +25756,10 @@
         <x:v>ANKLE_FOOT</x:v>
       </x:c>
       <x:c r="E11" s="9" t="str">
-        <x:v>软组织：足底筋膜内侧带
-肌群：拇展肌；趾短屈肌；长屈趾肌邻近</x:v>
+        <x:v>筋膜与表浅肌群：足底腱膜；拇展肌；趾短屈肌
+深层邻近：足底方肌；屈趾肌腱；足内在肌群
+相关肌腱：胫骨后肌腱；腓骨长肌腱
+骨与关节：跟骨至中前足的足弓结构</x:v>
       </x:c>
       <x:c r="F11" s="9" t="str">
         <x:v>AF-LT-007|AF-MUS-014|AF-MUS-016|CORE-CAP-ARCH-TOE|CORE-ROM-ANK-DF</x:v>
@@ -24213,8 +25800,9 @@
         <x:v>ANKLE_FOOT</x:v>
       </x:c>
       <x:c r="E12" s="9" t="str">
-        <x:v>骨与关节：舟骨；内侧中足关节
-肌腱：胫骨后肌止点</x:v>
+        <x:v>骨与关节：舟骨；内侧楔骨；邻近中足关节
+肌腱：胫骨后肌腱止点；胫骨前肌腱远端邻近
+足底邻近：拇展肌；足底筋膜与足弓支持组织</x:v>
       </x:c>
       <x:c r="F12" s="9" t="str">
         <x:v>AF-LT-008|CORE-MUS-TP|CORE-CAP-INV|CORE-CAP-PF|AF-JNT-003</x:v>
@@ -24255,8 +25843,9 @@
         <x:v>ANKLE_FOOT</x:v>
       </x:c>
       <x:c r="E13" s="9" t="str">
-        <x:v>骨与关节：第五跖骨基底；骰骨邻近
-肌腱：腓骨短肌止点；腓骨长肌邻近</x:v>
+        <x:v>骨与关节：第五跖骨基底；骰骨；外侧中足关节
+肌腱：腓骨短肌腱止点；第三腓骨肌腱；腓骨长肌腱走行
+足底邻近：小趾展肌；外侧足底筋膜</x:v>
       </x:c>
       <x:c r="F13" s="9" t="str">
         <x:v>AF-LT-009|CORE-MUS-PB|CORE-MUS-PL|CORE-ROM-ANK-INV|CORE-CAP-EV|AF-JNT-003</x:v>
@@ -24297,8 +25886,10 @@
         <x:v>ANKLE_FOOT</x:v>
       </x:c>
       <x:c r="E14" s="9" t="str">
-        <x:v>关节：跗跖及中足关节
-肌腱：胫骨前肌；拇长伸肌；趾长伸肌</x:v>
+        <x:v>肌腱：趾长伸肌腱；拇长伸肌腱；胫骨前肌腱邻近
+肌群：趾短伸肌；拇短伸肌
+骨与关节：跗骨背侧；跖骨基底；中足关节
+神经与支持组织：深腓神经；伸肌支持组织</x:v>
       </x:c>
       <x:c r="F14" s="9" t="str">
         <x:v>AF-LT-010|CORE-MUS-EHL|CORE-MUS-EDL|CORE-CAP-DF|AF-JNT-003</x:v>
@@ -24339,8 +25930,9 @@
         <x:v>ANKLE_FOOT</x:v>
       </x:c>
       <x:c r="E15" s="9" t="str">
-        <x:v>局部组织：第2–5跖骨头；跖板
-肌群：趾短屈肌；拇收肌；长屈趾肌邻近</x:v>
+        <x:v>骨与关节：第2–5跖骨头；跖趾关节；近节趾骨
+肌腱与肌群：屈趾肌腱；蚓状肌；骨间肌；趾短屈肌；小趾肌群
+周围组织：跖板；足底脂肪垫；趾间神经</x:v>
       </x:c>
       <x:c r="F15" s="9" t="str">
         <x:v>AF-LT-011|AF-JNT-005|AF-MUS-015|AF-MUS-016|CORE-CAP-ARCH-TOE</x:v>
@@ -24381,8 +25973,10 @@
         <x:v>ANKLE_FOOT</x:v>
       </x:c>
       <x:c r="E16" s="9" t="str">
-        <x:v>骨与关节：第一MTP；籽骨
-软组织：跖板；拇短屈肌；拇长屈肌腱邻近</x:v>
+        <x:v>骨与关节：第一跖骨头；拇趾近节趾骨；第一跖趾关节；籽骨
+肌腱：拇长屈肌腱；拇长伸肌腱
+肌群：拇短屈肌；拇展肌；拇收肌；拇短伸肌
+周围组织：跖板；关节囊</x:v>
       </x:c>
       <x:c r="F16" s="9" t="str">
         <x:v>AF-ASM-004|AF-LT-012|AF-MUS-017|CORE-CAP-HF</x:v>
@@ -24423,14 +26017,16 @@
         <x:v>THIGH</x:v>
       </x:c>
       <x:c r="E17" s="9" t="str">
-        <x:v>肌群：股直肌；股外侧肌；股内侧肌；股中间肌邻近
-局部组织：前侧肌筋膜；股骨邻近</x:v>
+        <x:v>肌肉：股直肌；股内侧肌；股外侧肌
+深层邻近：股中间肌
+斜行经过：缝匠肌
+骨与周围组织：股骨；股四头肌筋膜；远端股四头肌腱</x:v>
       </x:c>
       <x:c r="F17" s="9" t="str">
         <x:v>THIGH-LT-001|CORE-MUS-RF|CORE-MUS-VL|CORE-MUS-VM|KNEE-ROM-FLEX|CORE-CAP-KNEE-EXT</x:v>
       </x:c>
       <x:c r="G17" s="9" t="str">
-        <x:v>CORE-MUS-VI|KNEE-ROM-EXT</x:v>
+        <x:v>CORE-MUS-VI|KNEE-ROM-EXT|CORE-CAP-QUAD-RECRUIT|CORE-MUS-SART</x:v>
       </x:c>
       <x:c r="H17" s="9" t="str">
         <x:v>CORE-SPT-NEURO-DISTAL|THIGH-SPT-NEURO|THIGH-PATTERN-GAIT|THIGH-PATTERN-SAGITTAL|THIGH-PATTERN-LATERAL</x:v>
@@ -24463,8 +26059,9 @@
         <x:v>THIGH</x:v>
       </x:c>
       <x:c r="E18" s="9" t="str">
-        <x:v>肌群：股二头肌；半腱肌；半膜肌
-局部组织：后侧肌腱膜；坐骨近端邻近</x:v>
+        <x:v>肌肉：股二头肌长头与短头；半腱肌；半膜肌
+周围组织：腘绳肌腱膜及远端肌腱
+骨与深层邻近：股骨；坐骨神经</x:v>
       </x:c>
       <x:c r="F18" s="9" t="str">
         <x:v>THIGH-LT-002|CORE-MUS-BF|CORE-MUS-ST|CORE-MUS-SM|CORE-CAP-KNEE-FLEX|KNEE-ROM-EXT</x:v>
@@ -24503,14 +26100,16 @@
         <x:v>THIGH</x:v>
       </x:c>
       <x:c r="E19" s="9" t="str">
-        <x:v>肌群：内收长肌；内收短肌；内收大肌；股薄肌
-局部组织：内侧肌腱膜；股骨邻近</x:v>
+        <x:v>肌肉：内收长肌；内收大肌；股薄肌
+深层邻近：内收短肌；耻骨肌
+斜行经过：缝匠肌
+骨与周围组织：股骨内侧；内收肌筋膜；远端鹅足肌腱</x:v>
       </x:c>
       <x:c r="F19" s="9" t="str">
         <x:v>THIGH-LT-003|THIGH-MUS-AL|THIGH-MUS-AM|CORE-MUS-GRAC|THIGH-CAP-ADD</x:v>
       </x:c>
       <x:c r="G19" s="9" t="str">
-        <x:v>THIGH-MUS-AB|KNEE-ROM-EXT</x:v>
+        <x:v>THIGH-MUS-AB|KNEE-ROM-EXT|CORE-MUS-SART|KNEE-ROM-FLEX</x:v>
       </x:c>
       <x:c r="H19" s="9" t="str">
         <x:v>CORE-SPT-NEURO-DISTAL|THIGH-SPT-NEURO|THIGH-PATTERN-GAIT|THIGH-PATTERN-SAGITTAL|THIGH-PATTERN-LATERAL</x:v>
@@ -24543,8 +26142,9 @@
         <x:v>THIGH</x:v>
       </x:c>
       <x:c r="E20" s="9" t="str">
-        <x:v>肌群：股外侧肌；阔筋膜张肌邻近
-局部组织：髂胫束周围筋膜；股骨邻近</x:v>
+        <x:v>肌肉：股外侧肌；近端阔筋膜张肌
+筋膜与邻近肌群：髂胫束；后外侧股二头肌
+骨与远端邻近：股骨外侧；股骨外侧髁；膝外侧软组织</x:v>
       </x:c>
       <x:c r="F20" s="9" t="str">
         <x:v>THIGH-LT-004|THIGH-MUS-TFL|CORE-MUS-VL|KNEE-ROM-FLEX|CORE-CAP-KNEE-EXT</x:v>
@@ -24585,7 +26185,8 @@
       </x:c>
       <x:c r="E21" s="19" t="str">
         <x:v>肌腱：拇长伸肌腱；拇长屈肌腱
-根部关节：第一跖趾关节</x:v>
+肌群：拇短屈肌；拇展肌；拇收肌；拇短伸肌
+骨与关节：拇趾趾骨；第一跖趾关节；趾间关节</x:v>
       </x:c>
       <x:c r="F21" s="19" t="str">
         <x:v>CORE-MUS-EHL|CORE-MUS-FHL|AF-ASM-004|CORE-CAP-HF|CORE-CAP-ARCH-TOE</x:v>
@@ -24628,8 +26229,9 @@
         <x:v>ANKLE_FOOT</x:v>
       </x:c>
       <x:c r="E22" s="19" t="str">
-        <x:v>肌腱：趾长伸肌腱；趾长屈肌腱
-根部关节：第2–5跖趾关节</x:v>
+        <x:v>肌腱：第2–5趾伸肌腱与屈肌腱
+肌群：蚓状肌；骨间肌；趾短屈肌；小趾肌群
+骨与关节：第2–5趾骨；跖趾关节；趾间关节</x:v>
       </x:c>
       <x:c r="F22" s="19" t="str">
         <x:v>CORE-MUS-EDL|CORE-MUS-FDL|AF-JNT-005|CORE-CAP-ARCH-TOE</x:v>
@@ -24654,6 +26256,1517 @@
         <x:v>第2–5足趾定位入口复用既有长屈伸趾肌牵拉、抗阻、足趾控制及根部跖趾关节内容，不新增趾间关节、趾端或甲周问题。相关肌群检查不表示趾端疼痛来自肌腹。跖骨头与跖板局部组织仅为根部邻近参考。</x:v>
       </x:c>
       <x:c r="M22" s="22" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="210" customHeight="1">
+      <x:c r="A23" t="str">
+        <x:v>LOC-THIGH-ANTMED</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>大腿前内侧／股内侧肌邻近</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>THIGH-R-001</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>THIGH</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>肌肉：股内侧肌；邻近股直肌
+深层邻近：股中间肌
+斜行邻近：缝匠肌
+骨与远端邻近：股骨；股四头肌腱；髌骨内上缘</x:v>
+      </x:c>
+      <x:c r="F23" t="str">
+        <x:v>CORE-MUS-VM|CORE-MUS-RF|THIGH-LT-001|KNEE-ROM-FLEX|KNEE-ROM-EXT|CORE-CAP-KNEE-EXT|CORE-CAP-QUAD-RECRUIT</x:v>
+      </x:c>
+      <x:c r="G23" t="str">
+        <x:v>CORE-MUS-VL|CORE-MUS-VI|CORE-MUS-SART</x:v>
+      </x:c>
+      <x:c r="H23" t="str">
+        <x:v>CORE-SPT-NEURO-DISTAL|THIGH-SPT-NEURO|THIGH-PATTERN-GAIT|THIGH-PATTERN-SAGITTAL|THIGH-PATTERN-LATERAL</x:v>
+      </x:c>
+      <x:c r="I23" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J23" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K23" t="str">
+        <x:v>BodyParts3D 4.0 原始具名肌肉及骨骼；https://www.ncbi.nlm.nih.gov/books/NBK500008/
+既有02_ClinicalItem及05_RegionClinicalMap；定位子区域复用现有临床内容</x:v>
+      </x:c>
+      <x:c r="L23" t="str">
+        <x:v>体表定位子区域，具名肌肉用于模型标注参照，不能据此确定症状来源。复用已有肌群、关节、能力及局部组织项目；不新增诊断或处理方案。</x:v>
+      </x:c>
+      <x:c r="M23" s="20" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="210" customHeight="1">
+      <x:c r="A24" t="str">
+        <x:v>LOC-THIGH-ANTLAT</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>大腿前外侧／股外侧肌邻近</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>THIGH-R-001</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>THIGH</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>肌肉：股外侧肌；邻近股直肌
+深层邻近：股中间肌
+骨与筋膜：股骨；外侧肌间隔；外侧邻近髂胫束</x:v>
+      </x:c>
+      <x:c r="F24" t="str">
+        <x:v>CORE-MUS-VL|CORE-MUS-RF|THIGH-LT-001|KNEE-ROM-FLEX|CORE-CAP-KNEE-EXT</x:v>
+      </x:c>
+      <x:c r="G24" t="str">
+        <x:v>CORE-MUS-VM|CORE-MUS-VI|KNEE-ROM-EXT|CORE-CAP-QUAD-RECRUIT</x:v>
+      </x:c>
+      <x:c r="H24" t="str">
+        <x:v>CORE-SPT-NEURO-DISTAL|THIGH-SPT-NEURO|THIGH-PATTERN-GAIT|THIGH-PATTERN-SAGITTAL|THIGH-PATTERN-LATERAL</x:v>
+      </x:c>
+      <x:c r="I24" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J24" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K24" t="str">
+        <x:v>BodyParts3D 4.0 原始具名肌肉及骨骼；https://www.ncbi.nlm.nih.gov/books/NBK500008/
+既有02_ClinicalItem及05_RegionClinicalMap；定位子区域复用现有临床内容</x:v>
+      </x:c>
+      <x:c r="L24" t="str">
+        <x:v>体表定位子区域，具名肌肉用于模型标注参照，不能据此确定症状来源。复用已有肌群、关节、能力及局部组织项目；不新增诊断或处理方案。</x:v>
+      </x:c>
+      <x:c r="M24" s="20" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="210" customHeight="1">
+      <x:c r="A25" t="str">
+        <x:v>LOC-THIGH-POSTMED</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>大腿后内侧／内侧腘绳肌邻近</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>THIGH-R-002</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>THIGH</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>肌肉：半腱肌；半膜肌
+内侧邻近：股薄肌；内收大肌
+远端邻近：鹅足及膝后内侧肌腱
+骨与深层邻近：股骨；坐骨神经</x:v>
+      </x:c>
+      <x:c r="F25" t="str">
+        <x:v>CORE-MUS-ST|CORE-MUS-SM|THIGH-LT-002|KNEE-ROM-EXT|CORE-CAP-KNEE-FLEX</x:v>
+      </x:c>
+      <x:c r="G25" t="str">
+        <x:v>CORE-MUS-BF|KNEE-ROM-FLEX</x:v>
+      </x:c>
+      <x:c r="H25" t="str">
+        <x:v>THIGH-SPT-NEURO|THIGH-PATTERN-GAIT|THIGH-PATTERN-SAGITTAL|THIGH-PATTERN-LATERAL</x:v>
+      </x:c>
+      <x:c r="I25" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J25" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K25" t="str">
+        <x:v>BodyParts3D 4.0 原始具名肌肉及骨骼；https://www.ncbi.nlm.nih.gov/books/NBK500008/
+既有02_ClinicalItem及05_RegionClinicalMap；定位子区域复用现有临床内容</x:v>
+      </x:c>
+      <x:c r="L25" t="str">
+        <x:v>体表定位子区域，具名肌肉用于模型标注参照，不能据此确定症状来源。复用已有肌群、关节、能力及局部组织项目；不新增诊断或处理方案。</x:v>
+      </x:c>
+      <x:c r="M25" s="20" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="210" customHeight="1">
+      <x:c r="A26" t="str">
+        <x:v>LOC-THIGH-POSTLAT</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>大腿后外侧／股二头肌邻近</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>THIGH-R-002</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>THIGH</x:v>
+      </x:c>
+      <x:c r="E26" t="str">
+        <x:v>肌肉：股二头肌长头与短头
+前外侧邻近：股外侧肌；髂胫束
+远端邻近：股二头肌腱；腓骨头
+深层邻近：坐骨神经</x:v>
+      </x:c>
+      <x:c r="F26" t="str">
+        <x:v>CORE-MUS-BF|THIGH-LT-002|KNEE-ROM-EXT|CORE-CAP-KNEE-FLEX</x:v>
+      </x:c>
+      <x:c r="G26" t="str">
+        <x:v>CORE-MUS-ST|CORE-MUS-SM|KNEE-ROM-FLEX</x:v>
+      </x:c>
+      <x:c r="H26" t="str">
+        <x:v>THIGH-SPT-NEURO|THIGH-PATTERN-GAIT|THIGH-PATTERN-SAGITTAL|THIGH-PATTERN-LATERAL</x:v>
+      </x:c>
+      <x:c r="I26" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J26" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K26" t="str">
+        <x:v>BodyParts3D 4.0 原始具名肌肉及骨骼；https://www.ncbi.nlm.nih.gov/books/NBK500008/
+既有02_ClinicalItem及05_RegionClinicalMap；定位子区域复用现有临床内容</x:v>
+      </x:c>
+      <x:c r="L26" t="str">
+        <x:v>体表定位子区域，具名肌肉用于模型标注参照，不能据此确定症状来源。复用已有肌群、关节、能力及局部组织项目；不新增诊断或处理方案。</x:v>
+      </x:c>
+      <x:c r="M26" s="20" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="210" customHeight="1">
+      <x:c r="A27" t="str">
+        <x:v>LOC-THIGH-SART</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>大腿斜行／缝匠肌邻近</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>THIGH-R-001|THIGH-R-003</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>THIGH</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>斜行肌肉：缝匠肌
+前侧邻近：股直肌；股内侧肌
+内侧邻近：股薄肌；内收肌群
+远端邻近：鹅足肌腱</x:v>
+      </x:c>
+      <x:c r="F27" t="str">
+        <x:v>CORE-MUS-SART|THIGH-LT-001|THIGH-LT-003|KNEE-ROM-FLEX|KNEE-ROM-EXT</x:v>
+      </x:c>
+      <x:c r="G27" t="str">
+        <x:v>CORE-MUS-RF|CORE-MUS-VM|CORE-MUS-GRAC|THIGH-MUS-AL|CORE-CAP-KNEE-FLEX|CORE-CAP-KNEE-EXT</x:v>
+      </x:c>
+      <x:c r="H27" t="str">
+        <x:v>CORE-SPT-NEURO-DISTAL|THIGH-SPT-NEURO|THIGH-PATTERN-GAIT|THIGH-PATTERN-SAGITTAL|THIGH-PATTERN-LATERAL</x:v>
+      </x:c>
+      <x:c r="I27" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J27" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K27" t="str">
+        <x:v>BodyParts3D 4.0 原始具名肌肉及骨骼；https://www.ncbi.nlm.nih.gov/books/NBK500008/
+既有02_ClinicalItem及05_RegionClinicalMap；定位子区域复用现有临床内容</x:v>
+      </x:c>
+      <x:c r="L27" t="str">
+        <x:v>体表定位子区域，具名肌肉用于模型标注参照，不能据此确定症状来源。复用已有肌群、关节、能力及局部组织项目；不新增诊断或处理方案。</x:v>
+      </x:c>
+      <x:c r="M27" s="20" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="210" customHeight="1">
+      <x:c r="A28" t="str">
+        <x:v>LOC-KNEE-R-001</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>髌骨上缘与股四头肌腱</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>KNEE-R-001</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>KNEE</x:v>
+      </x:c>
+      <x:c r="E28" t="str">
+        <x:v>肌肉与肌腱：股四头肌远端；股四头肌腱
+骨与关节：髌骨上缘；髌股关节
+周围组织：髌上囊</x:v>
+      </x:c>
+      <x:c r="F28" t="str">
+        <x:v>CORE-MUS-RF|CORE-MUS-VM|CORE-MUS-VL|KNEE-LT-SUPRAPAT|KNEE-ROM-EXT|KNEE-ROM-FLEX|KNEE-JNT-PF|CORE-CAP-QUAD-RECRUIT|CORE-CAP-KNEE-EXT</x:v>
+      </x:c>
+      <x:c r="G28" t="str">
+        <x:v>CORE-MUS-VI|KNEE-MUS-HIPFLEX|KNEE-MUS-LAT-CHAIN|CORE-MUS-BF|KNEE-CAP-HIPEXT|KNEE-CAP-HIPABD|KNEE-LT-PATELLA</x:v>
+      </x:c>
+      <x:c r="H28" t="str">
+        <x:v>KNEE-PATTERN-GAIT|KNEE-PATTERN-BILATERAL|KNEE-PATTERN-SINGLE|KNEE-PATTERN-LANDING|KNEE-PATTERN-DIRECTION|KNEE-SPT-MECH|CORE-SPT-NEURO-DISTAL|KNEE-CHAIN-HIP-ROM|CORE-ROM-ANK-DF</x:v>
+      </x:c>
+      <x:c r="I28" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J28" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K28" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验膝部主动活动与抗阻章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L28" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M28" s="20" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="210" customHeight="1">
+      <x:c r="A29" t="str">
+        <x:v>LOC-KNEE-R-002</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>髌骨外侧缘</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>KNEE-R-002</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>KNEE</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>肌肉与肌腱：股外侧肌远端；股四头肌腱外侧部分
+周围组织：髌骨外侧支持带
+骨与关节：髌骨外侧缘；髌股关节</x:v>
+      </x:c>
+      <x:c r="F29" t="str">
+        <x:v>CORE-MUS-VL|KNEE-LT-PATELLA|KNEE-ROM-EXT|KNEE-ROM-FLEX|KNEE-JNT-PF|CORE-CAP-QUAD-RECRUIT|CORE-CAP-KNEE-EXT</x:v>
+      </x:c>
+      <x:c r="G29" t="str">
+        <x:v>CORE-MUS-RF|CORE-MUS-VI|KNEE-MUS-LAT-CHAIN|KNEE-MUS-HIPFLEX|CORE-CAP-KNEE-FLEX|KNEE-CAP-HIPABD|KNEE-CAP-HIPEXT</x:v>
+      </x:c>
+      <x:c r="H29" t="str">
+        <x:v>CORE-MUS-GASTROC|CORE-MUS-SOLEUS|KNEE-SPT-MECH|CORE-SPT-NEURO-DISTAL|KNEE-CHAIN-HIP-ROM|CORE-ROM-ANK-DF</x:v>
+      </x:c>
+      <x:c r="I29" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J29" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K29" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验膝部主动活动与抗阻章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L29" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M29" s="20" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="210" customHeight="1">
+      <x:c r="A30" t="str">
+        <x:v>LOC-KNEE-R-003</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>髌骨内侧缘</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>KNEE-R-003</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>KNEE</x:v>
+      </x:c>
+      <x:c r="E30" t="str">
+        <x:v>肌肉与肌腱：股内侧肌远端；股四头肌腱内侧部分
+周围组织：髌骨内侧支持带；内侧髌股韧带
+骨与关节：髌骨内侧缘；髌股关节</x:v>
+      </x:c>
+      <x:c r="F30" t="str">
+        <x:v>CORE-MUS-VM|KNEE-LT-PATELLA|KNEE-ROM-EXT|KNEE-ROM-FLEX|KNEE-JNT-PF|CORE-CAP-QUAD-RECRUIT|CORE-CAP-KNEE-EXT</x:v>
+      </x:c>
+      <x:c r="G30" t="str">
+        <x:v>CORE-MUS-RF|CORE-MUS-VL|CORE-MUS-VI|KNEE-MUS-ADD|CORE-CAP-KNEE-FLEX|CORE-MUS-SM|KNEE-MUS-HIPFLEX|KNEE-CAP-HIPABD|KNEE-CAP-HIPEXT</x:v>
+      </x:c>
+      <x:c r="H30" t="str">
+        <x:v>KNEE-SPT-MECH|CORE-SPT-NEURO-DISTAL|KNEE-CHAIN-HIP-ROM|CORE-ROM-ANK-DF</x:v>
+      </x:c>
+      <x:c r="I30" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J30" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K30" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验膝部主动活动与抗阻章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L30" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M30" s="20" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="210" customHeight="1">
+      <x:c r="A31" t="str">
+        <x:v>LOC-KNEE-R-004</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>髌骨前方</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>KNEE-R-004</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>KNEE</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>骨与关节：髌骨；深部髌股关节
+表浅组织：髌前滑囊；皮下组织
+周围组织：髌骨支持带</x:v>
+      </x:c>
+      <x:c r="F31" t="str">
+        <x:v>KNEE-LT-PATELLA|KNEE-ROM-EXT|KNEE-ROM-FLEX|KNEE-JNT-PF|CORE-CAP-QUAD-RECRUIT|CORE-CAP-KNEE-EXT</x:v>
+      </x:c>
+      <x:c r="G31" t="str">
+        <x:v>CORE-MUS-RF|CORE-MUS-VM|CORE-MUS-VL|CORE-MUS-VI|KNEE-MUS-HIPFLEX|KNEE-MUS-LAT-CHAIN|CORE-MUS-BF|KNEE-CAP-HIPEXT|KNEE-CAP-HIPABD|CORE-CAP-KNEE-FLEX</x:v>
+      </x:c>
+      <x:c r="H31" t="str">
+        <x:v>CORE-MUS-GASTROC|CORE-MUS-SOLEUS|KNEE-SPT-MECH|CORE-SPT-NEURO-DISTAL|KNEE-CHAIN-HIP-ROM|CORE-ROM-ANK-DF</x:v>
+      </x:c>
+      <x:c r="I31" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J31" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K31" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验膝部主动活动与抗阻章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L31" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M31" s="20" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="210" customHeight="1">
+      <x:c r="A32" t="str">
+        <x:v>LOC-KNEE-R-005</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>髌骨下缘与髌腱近端</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>KNEE-R-005</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>KNEE</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>骨与肌腱：髌骨下缘；髌腱近端
+深部邻近：髌下脂肪垫；膝前关节囊</x:v>
+      </x:c>
+      <x:c r="F32" t="str">
+        <x:v>KNEE-LT-INFRAPAT|KNEE-ROM-EXT|KNEE-ROM-FLEX|CORE-CAP-QUAD-RECRUIT|CORE-CAP-KNEE-EXT</x:v>
+      </x:c>
+      <x:c r="G32" t="str">
+        <x:v>CORE-MUS-RF|CORE-MUS-VL|CORE-MUS-VI|KNEE-MUS-HIPFLEX|CORE-MUS-GASTROC|KNEE-CAP-HIPEXT|KNEE-CAP-HIPABD|CORE-CAP-KNEE-FLEX|KNEE-JNT-PF|KNEE-LT-PATELLA</x:v>
+      </x:c>
+      <x:c r="H32" t="str">
+        <x:v>CORE-MUS-SOLEUS|CORE-MUS-ST|KNEE-SPT-MECH|CORE-SPT-NEURO-DISTAL|KNEE-CHAIN-HIP-ROM|CORE-ROM-ANK-DF</x:v>
+      </x:c>
+      <x:c r="I32" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J32" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K32" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验膝部主动活动与抗阻章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L32" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M32" s="20" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="210" customHeight="1">
+      <x:c r="A33" t="str">
+        <x:v>LOC-KNEE-R-006</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>髌下前方</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>KNEE-R-006</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>KNEE</x:v>
+      </x:c>
+      <x:c r="E33" t="str">
+        <x:v>肌腱与骨：髌腱；髌骨下缘；胫骨结节
+周围组织：髌下浅滑囊；髌下深滑囊；髌下脂肪垫</x:v>
+      </x:c>
+      <x:c r="F33" t="str">
+        <x:v>KNEE-LT-INFRAPAT|KNEE-ROM-EXT|KNEE-ROM-FLEX|CORE-CAP-QUAD-RECRUIT|CORE-CAP-KNEE-EXT</x:v>
+      </x:c>
+      <x:c r="G33" t="str">
+        <x:v>CORE-MUS-RF|CORE-MUS-VL|CORE-MUS-VI|KNEE-MUS-HIPFLEX|CORE-MUS-GASTROC|KNEE-CAP-HIPEXT|KNEE-CAP-HIPABD|CORE-CAP-KNEE-FLEX|KNEE-JNT-PF</x:v>
+      </x:c>
+      <x:c r="H33" t="str">
+        <x:v>CORE-MUS-SOLEUS|CORE-MUS-ST|KNEE-SPT-MECH|CORE-SPT-NEURO-DISTAL|KNEE-CHAIN-HIP-ROM|CORE-ROM-ANK-DF</x:v>
+      </x:c>
+      <x:c r="I33" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J33" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K33" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验膝部主动活动与抗阻章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L33" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M33" s="20" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="210" customHeight="1">
+      <x:c r="A34" t="str">
+        <x:v>LOC-KNEE-PATELLAR-TENDON</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>髌腱邻近</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>KNEE-R-006</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>KNEE</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>肌腱与附着：髌腱；髌骨下缘；胫骨结节
+深部邻近：髌下脂肪垫；髌下滑囊</x:v>
+      </x:c>
+      <x:c r="F34" t="str">
+        <x:v>KNEE-LT-INFRAPAT|KNEE-ROM-EXT|KNEE-ROM-FLEX|CORE-CAP-QUAD-RECRUIT|CORE-CAP-KNEE-EXT</x:v>
+      </x:c>
+      <x:c r="G34" t="str">
+        <x:v>CORE-MUS-RF|CORE-MUS-VL|CORE-MUS-VI|KNEE-MUS-HIPFLEX|CORE-MUS-GASTROC|KNEE-CAP-HIPEXT|KNEE-CAP-HIPABD|CORE-CAP-KNEE-FLEX|KNEE-JNT-PF</x:v>
+      </x:c>
+      <x:c r="H34" t="str">
+        <x:v>CORE-MUS-SOLEUS|CORE-MUS-ST|KNEE-SPT-MECH|CORE-SPT-NEURO-DISTAL|KNEE-CHAIN-HIP-ROM|CORE-ROM-ANK-DF</x:v>
+      </x:c>
+      <x:c r="I34" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J34" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K34" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验膝部主动活动与抗阻章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L34" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M34" s="20" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="210" customHeight="1">
+      <x:c r="A35" t="str">
+        <x:v>LOC-KNEE-TIBIAL-TUBERCLE</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>胫骨结节邻近</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>KNEE-R-006</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>KNEE</x:v>
+      </x:c>
+      <x:c r="E35" t="str">
+        <x:v>骨与附着：胫骨结节；髌腱止点
+周围组织：髌下滑囊；皮下组织</x:v>
+      </x:c>
+      <x:c r="F35" t="str">
+        <x:v>KNEE-LT-INFRAPAT|KNEE-ROM-EXT|KNEE-ROM-FLEX|CORE-CAP-QUAD-RECRUIT|CORE-CAP-KNEE-EXT</x:v>
+      </x:c>
+      <x:c r="G35" t="str">
+        <x:v>CORE-MUS-RF|CORE-MUS-VL|CORE-MUS-VI|KNEE-MUS-HIPFLEX|CORE-MUS-GASTROC|KNEE-CAP-HIPEXT|KNEE-CAP-HIPABD|CORE-CAP-KNEE-FLEX|KNEE-JNT-PF</x:v>
+      </x:c>
+      <x:c r="H35" t="str">
+        <x:v>CORE-MUS-SOLEUS|CORE-MUS-ST|KNEE-SPT-MECH|CORE-SPT-NEURO-DISTAL|KNEE-CHAIN-HIP-ROM|CORE-ROM-ANK-DF</x:v>
+      </x:c>
+      <x:c r="I35" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J35" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K35" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验膝部主动活动与抗阻章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L35" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M35" s="20" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="210" customHeight="1">
+      <x:c r="A36" t="str">
+        <x:v>LOC-KNEE-R-007</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>膝内侧关节线</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>KNEE-R-007</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>KNEE</x:v>
+      </x:c>
+      <x:c r="E36" t="str">
+        <x:v>关节与韧带：膝内侧关节囊；内侧副韧带
+深部邻近：内侧半月板
+骨：股骨内侧髁；胫骨内侧平台</x:v>
+      </x:c>
+      <x:c r="F36" t="str">
+        <x:v>KNEE-LT-MEDIAL|KNEE-ROM-EXT|KNEE-ROM-FLEX|KNEE-JNT-TIBROT</x:v>
+      </x:c>
+      <x:c r="G36" t="str">
+        <x:v>CORE-MUS-SM|CORE-MUS-ST|CORE-MUS-VM|CORE-CAP-KNEE-FLEX|KNEE-MUS-ADD|CORE-CAP-QUAD-RECRUIT|CORE-MUS-RF|CORE-MUS-GASTROC|KNEE-CAP-HIPABD|KNEE-CAP-HIPEXT|CORE-CAP-KNEE-EXT|KNEE-JNT-PROXTF</x:v>
+      </x:c>
+      <x:c r="H36" t="str">
+        <x:v>CORE-MUS-SOLEUS|KNEE-SPT-MECH|CORE-SPT-NEURO-DISTAL|KNEE-CHAIN-HIP-ROM|CORE-ROM-ANK-DF</x:v>
+      </x:c>
+      <x:c r="I36" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J36" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K36" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验膝部主动活动与抗阻章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L36" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M36" s="20" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="210" customHeight="1">
+      <x:c r="A37" t="str">
+        <x:v>LOC-KNEE-R-008</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>鹅足区 / 膝下内侧</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>KNEE-R-008</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>KNEE</x:v>
+      </x:c>
+      <x:c r="E37" t="str">
+        <x:v>肌肉与肌腱：缝匠肌腱；股薄肌腱；半腱肌腱
+周围组织：鹅足滑囊；内侧副韧带邻近
+骨：胫骨近端内侧</x:v>
+      </x:c>
+      <x:c r="F37" t="str">
+        <x:v>CORE-MUS-SART|CORE-MUS-GRAC|CORE-MUS-ST|KNEE-LT-MEDIAL|KNEE-ROM-EXT|KNEE-ROM-FLEX|KNEE-CAP-PES</x:v>
+      </x:c>
+      <x:c r="G37" t="str">
+        <x:v>CORE-CAP-KNEE-FLEX|KNEE-MUS-ADD|CORE-MUS-SM|CORE-MUS-VM|CORE-MUS-RF|CORE-MUS-GASTROC|KNEE-CAP-HIPABD|KNEE-CAP-HIPEXT|CORE-CAP-KNEE-EXT|KNEE-JNT-TIBROT|KNEE-JNT-PF</x:v>
+      </x:c>
+      <x:c r="H37" t="str">
+        <x:v>CORE-MUS-SOLEUS|KNEE-SPT-MECH|CORE-SPT-NEURO-DISTAL|KNEE-CHAIN-HIP-ROM|CORE-ROM-ANK-DF</x:v>
+      </x:c>
+      <x:c r="I37" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J37" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K37" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验膝部主动活动与抗阻章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L37" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M37" s="20" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="210" customHeight="1">
+      <x:c r="A38" t="str">
+        <x:v>LOC-KNEE-R-009</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>膝后内侧／内侧腘绳肌腱邻近</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>KNEE-R-009</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>KNEE</x:v>
+      </x:c>
+      <x:c r="E38" t="str">
+        <x:v>肌肉与肌腱：半膜肌远端；半腱肌腱；腓肠肌内侧头
+周围组织：后内侧关节囊；半膜肌与腓肠肌之间的滑囊
+浅表邻近：缝匠肌腱；股薄肌腱</x:v>
+      </x:c>
+      <x:c r="F38" t="str">
+        <x:v>CORE-MUS-SM|CORE-MUS-ST|CORE-MUS-GASTROC|KNEE-LT-POST|KNEE-ROM-EXT|KNEE-ROM-FLEX|CORE-CAP-KNEE-FLEX</x:v>
+      </x:c>
+      <x:c r="G38" t="str">
+        <x:v>KNEE-MUS-ADD|CORE-CAP-PF|KNEE-MUS-POPLIT|CORE-MUS-VM|KNEE-CAP-HIPEXT|KNEE-CAP-HIPABD|KNEE-LT-MEDIAL|KNEE-JNT-TIBROT|KNEE-JNT-PROXTF</x:v>
+      </x:c>
+      <x:c r="H38" t="str">
+        <x:v>KNEE-SPT-MECH|CORE-SPT-NEURO-DISTAL|KNEE-CHAIN-HIP-ROM|CORE-ROM-ANK-DF</x:v>
+      </x:c>
+      <x:c r="I38" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J38" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K38" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验膝部主动活动与抗阻章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L38" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M38" s="20" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="210" customHeight="1">
+      <x:c r="A39" t="str">
+        <x:v>LOC-KNEE-R-010</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>膝外侧关节线</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>KNEE-R-010</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>KNEE</x:v>
+      </x:c>
+      <x:c r="E39" t="str">
+        <x:v>关节与韧带：膝外侧关节囊；外侧副韧带
+深部邻近：外侧半月板；腘肌腱
+骨：股骨外侧髁；胫骨外侧平台</x:v>
+      </x:c>
+      <x:c r="F39" t="str">
+        <x:v>KNEE-LT-LATERAL|KNEE-ROM-EXT|KNEE-ROM-FLEX|KNEE-JNT-TIBROT</x:v>
+      </x:c>
+      <x:c r="G39" t="str">
+        <x:v>CORE-MUS-BF|KNEE-MUS-POPLIT|CORE-MUS-VL|CORE-CAP-KNEE-FLEX|KNEE-MUS-LAT-CHAIN|CORE-CAP-EV|CORE-MUS-RF|CORE-MUS-GASTROC|KNEE-CAP-HIPABD|KNEE-CAP-HIPEXT|CORE-CAP-KNEE-EXT|CORE-CAP-QUAD-RECRUIT|KNEE-JNT-PROXTF</x:v>
+      </x:c>
+      <x:c r="H39" t="str">
+        <x:v>CORE-MUS-SOLEUS|KNEE-SPT-MECH|CORE-SPT-NEURO-DISTAL|KNEE-CHAIN-HIP-ROM|CORE-ROM-ANK-DF</x:v>
+      </x:c>
+      <x:c r="I39" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J39" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K39" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验膝部主动活动与抗阻章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L39" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M39" s="20" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="210" customHeight="1">
+      <x:c r="A40" t="str">
+        <x:v>LOC-KNEE-R-011</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>腓骨头及肌腱附着邻近</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>KNEE-R-011</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>KNEE</x:v>
+      </x:c>
+      <x:c r="E40" t="str">
+        <x:v>骨与关节：腓骨头；近端胫腓关节
+肌腱与韧带：股二头肌腱止点；外侧副韧带止点
+神经与肌群：腓总神经；腓骨长肌近端</x:v>
+      </x:c>
+      <x:c r="F40" t="str">
+        <x:v>CORE-MUS-BF|CORE-MUS-PL|KNEE-LT-LATERAL|KNEE-JNT-PROXTF|KNEE-ROM-EXT|KNEE-ROM-FLEX|CORE-CAP-KNEE-FLEX|CORE-CAP-EV</x:v>
+      </x:c>
+      <x:c r="G40" t="str">
+        <x:v>KNEE-MUS-LAT-CHAIN|CORE-CAP-PF|CORE-MUS-VL|KNEE-CAP-HIPABD|KNEE-CAP-HIPEXT</x:v>
+      </x:c>
+      <x:c r="H40" t="str">
+        <x:v>KNEE-SPT-MECH|CORE-SPT-NEURO-DISTAL|KNEE-CHAIN-HIP-ROM|CORE-ROM-ANK-DF</x:v>
+      </x:c>
+      <x:c r="I40" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J40" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K40" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验膝部主动活动与抗阻章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L40" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M40" s="20" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="210" customHeight="1">
+      <x:c r="A41" t="str">
+        <x:v>LOC-KNEE-R-012</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>膝外侧／髂胫束远端邻近</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>KNEE-R-012</x:v>
+      </x:c>
+      <x:c r="D41" t="str">
+        <x:v>KNEE</x:v>
+      </x:c>
+      <x:c r="E41" t="str">
+        <x:v>软组织：髂胫束远端；外侧支持带
+骨与关节：股骨外侧髁；膝外侧关节囊
+肌群邻近：股外侧肌远端</x:v>
+      </x:c>
+      <x:c r="F41" t="str">
+        <x:v>CORE-MUS-VL|KNEE-MUS-LAT-CHAIN|KNEE-LT-LATERAL|KNEE-ROM-EXT|KNEE-ROM-FLEX|KNEE-CAP-HIPABD</x:v>
+      </x:c>
+      <x:c r="G41" t="str">
+        <x:v>KNEE-CAP-HIPEXT|CORE-CAP-KNEE-FLEX|CORE-MUS-RF|KNEE-MUS-HIPFLEX|CORE-MUS-GASTROC|CORE-CAP-KNEE-EXT|CORE-CAP-EV|CORE-CAP-QUAD-RECRUIT|KNEE-JNT-PROXTF</x:v>
+      </x:c>
+      <x:c r="H41" t="str">
+        <x:v>CORE-MUS-SOLEUS|KNEE-SPT-MECH|CORE-SPT-NEURO-DISTAL|KNEE-CHAIN-HIP-ROM|CORE-ROM-ANK-DF</x:v>
+      </x:c>
+      <x:c r="I41" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J41" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K41" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验膝部主动活动与抗阻章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L41" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M41" s="20" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="210" customHeight="1">
+      <x:c r="A42" t="str">
+        <x:v>LOC-KNEE-R-013</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>腘窝／膝后中央</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>KNEE-R-013</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>KNEE</x:v>
+      </x:c>
+      <x:c r="E42" t="str">
+        <x:v>肌肉与肌腱：腓肠肌近端；腘肌；腘绳肌远端
+关节与周围组织：膝后关节囊；腘窝脂肪与结缔组织
+神经与血管：胫神经；腘动脉；腘静脉</x:v>
+      </x:c>
+      <x:c r="F42" t="str">
+        <x:v>KNEE-LT-POST|CORE-MUS-GASTROC|KNEE-MUS-POPLIT|KNEE-ROM-EXT|KNEE-ROM-FLEX|CORE-CAP-KNEE-FLEX|CORE-CAP-PF</x:v>
+      </x:c>
+      <x:c r="G42" t="str">
+        <x:v>CORE-MUS-ST|CORE-MUS-SM|CORE-MUS-BF|KNEE-CAP-HIPEXT</x:v>
+      </x:c>
+      <x:c r="H42" t="str">
+        <x:v>KNEE-SPT-MECH|CORE-SPT-NEURO-DISTAL|KNEE-CHAIN-HIP-ROM|CORE-ROM-ANK-DF</x:v>
+      </x:c>
+      <x:c r="I42" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J42" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K42" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验膝部主动活动与抗阻章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L42" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M42" s="20" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="210" customHeight="1">
+      <x:c r="A43" t="str">
+        <x:v>LOC-KNEE-R-014</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>膝后外侧／股二头肌腱邻近</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>KNEE-R-014</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>KNEE</x:v>
+      </x:c>
+      <x:c r="E43" t="str">
+        <x:v>肌肉与肌腱：股二头肌腱；腓肠肌外侧头；腘肌腱
+关节与韧带：近端胫腓关节；外侧副韧带；后外侧关节囊
+神经与骨：腓总神经；腓骨头</x:v>
+      </x:c>
+      <x:c r="F43" t="str">
+        <x:v>CORE-MUS-BF|CORE-MUS-GASTROC|KNEE-MUS-POPLIT|KNEE-LT-POST|KNEE-ROM-EXT|KNEE-ROM-FLEX|KNEE-JNT-PROXTF|CORE-CAP-KNEE-FLEX</x:v>
+      </x:c>
+      <x:c r="G43" t="str">
+        <x:v>CORE-CAP-EV|CORE-CAP-PF|KNEE-MUS-LAT-CHAIN|CORE-MUS-SM|KNEE-CAP-HIPEXT|KNEE-CAP-HIPABD</x:v>
+      </x:c>
+      <x:c r="H43" t="str">
+        <x:v>KNEE-SPT-MECH|CORE-SPT-NEURO-DISTAL|KNEE-CHAIN-HIP-ROM|CORE-ROM-ANK-DF</x:v>
+      </x:c>
+      <x:c r="I43" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J43" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K43" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验膝部主动活动与抗阻章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L43" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M43" s="20" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="210" customHeight="1">
+      <x:c r="A44" t="str">
+        <x:v>LOC-AF-R-001</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>前踝关节与伸肌腱邻近</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>AF-R-001</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
+        <x:v>ANKLE_FOOT</x:v>
+      </x:c>
+      <x:c r="E44" t="str">
+        <x:v>肌腱：胫骨前肌腱；拇长伸肌腱；趾长伸肌腱
+关节与软组织：距小腿关节前方关节囊；伸肌支持带
+骨：胫骨远端；距骨</x:v>
+      </x:c>
+      <x:c r="F44" t="str">
+        <x:v>AF-LT-001|CORE-MUS-TA|CORE-MUS-EHL|CORE-MUS-EDL|CORE-ROM-ANK-DF|CORE-ROM-ANK-PF|AF-ASM-002|CORE-CAP-DF</x:v>
+      </x:c>
+      <x:c r="G44" t="str">
+        <x:v>CORE-MUS-SOLEUS|CORE-MUS-GASTROC|CORE-ROM-ANK-EV|CORE-ROM-ANK-INV</x:v>
+      </x:c>
+      <x:c r="H44" t="str">
+        <x:v>CORE-MUS-PT|AF-SPT-003|CORE-SPT-NEURO-DISTAL</x:v>
+      </x:c>
+      <x:c r="I44" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J44" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K44" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验踝足主动活动、抗阻及附属活动章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L44" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M44" s="20" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="210" customHeight="1">
+      <x:c r="A45" t="str">
+        <x:v>LOC-AF-R-002</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>内踝周围</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>AF-R-002</x:v>
+      </x:c>
+      <x:c r="D45" t="str">
+        <x:v>ANKLE_FOOT</x:v>
+      </x:c>
+      <x:c r="E45" t="str">
+        <x:v>韧带：三角韧带
+肌腱：胫骨后肌腱；趾长屈肌腱；拇长屈肌腱
+神经与血管：跗管内胫神经；胫后血管
+骨：内踝</x:v>
+      </x:c>
+      <x:c r="F45" t="str">
+        <x:v>AF-LT-002|CORE-MUS-TP|CORE-MUS-FDL|CORE-MUS-FHL|CORE-ROM-ANK-DF|CORE-ROM-ANK-EV|CORE-CAP-INV</x:v>
+      </x:c>
+      <x:c r="G45" t="str">
+        <x:v>CORE-CAP-HF|CORE-MUS-SOLEUS|CORE-MUS-GASTROC|AF-JNT-002|CORE-ROM-ANK-INV|CORE-CAP-ARCH-TOE</x:v>
+      </x:c>
+      <x:c r="H45" t="str">
+        <x:v>CORE-SPT-NEURO-DISTAL</x:v>
+      </x:c>
+      <x:c r="I45" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J45" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K45" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验踝足主动活动、抗阻及附属活动章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L45" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M45" s="20" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="210" customHeight="1">
+      <x:c r="A46" t="str">
+        <x:v>LOC-AF-MEDIAL-TENDONS</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>内踝后方／屈肌腱邻近</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>AF-R-002</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>ANKLE_FOOT</x:v>
+      </x:c>
+      <x:c r="E46" t="str">
+        <x:v>肌腱：胫骨后肌腱；趾长屈肌腱；拇长屈肌腱
+骨与通道：内踝后方；跗管
+周围组织：屈肌支持带；胫神经邻近</x:v>
+      </x:c>
+      <x:c r="F46" t="str">
+        <x:v>CORE-MUS-TP|CORE-MUS-FDL|CORE-MUS-FHL|AF-LT-002|CORE-ROM-ANK-DF|CORE-ROM-ANK-EV|CORE-CAP-INV|CORE-CAP-HF</x:v>
+      </x:c>
+      <x:c r="G46" t="str">
+        <x:v>CORE-MUS-SOLEUS|CORE-MUS-GASTROC|AF-JNT-002|CORE-ROM-ANK-INV|CORE-CAP-ARCH-TOE</x:v>
+      </x:c>
+      <x:c r="H46" t="str">
+        <x:v>CORE-SPT-NEURO-DISTAL</x:v>
+      </x:c>
+      <x:c r="I46" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J46" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K46" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验踝足主动活动、抗阻及附属活动章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L46" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M46" s="20" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="210" customHeight="1">
+      <x:c r="A47" t="str">
+        <x:v>LOC-AF-R-003</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>外踝周围</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>AF-R-003</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
+        <x:v>ANKLE_FOOT</x:v>
+      </x:c>
+      <x:c r="E47" t="str">
+        <x:v>韧带：距腓前韧带；跟腓韧带；距腓后韧带
+肌腱：腓骨长肌腱；腓骨短肌腱
+骨与关节：外踝；距骨邻近；距小腿关节</x:v>
+      </x:c>
+      <x:c r="F47" t="str">
+        <x:v>AF-LT-003|CORE-MUS-PL|CORE-MUS-PB|CORE-ROM-ANK-DF|CORE-ROM-ANK-INV|CORE-ROM-ANK-EV|AF-JNT-002|CORE-CAP-EV</x:v>
+      </x:c>
+      <x:c r="G47" t="str"/>
+      <x:c r="H47" t="str">
+        <x:v>CORE-MUS-PT|CORE-MUS-EDL|AF-TASK-001|AF-SPT-001|AF-SPT-002|AF-SPT-003|CORE-SPT-NEURO-DISTAL</x:v>
+      </x:c>
+      <x:c r="I47" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J47" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K47" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验踝足主动活动、抗阻及附属活动章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L47" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M47" s="20" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="210" customHeight="1">
+      <x:c r="A48" t="str">
+        <x:v>LOC-AF-LATERAL-TENDONS</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>外踝后方／腓骨肌腱邻近</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>AF-R-003</x:v>
+      </x:c>
+      <x:c r="D48" t="str">
+        <x:v>ANKLE_FOOT</x:v>
+      </x:c>
+      <x:c r="E48" t="str">
+        <x:v>肌腱：腓骨长肌腱；腓骨短肌腱
+骨与周围组织：外踝后方；腓骨肌支持带
+邻近：跟腓韧带；腓骨远端</x:v>
+      </x:c>
+      <x:c r="F48" t="str">
+        <x:v>CORE-MUS-PL|CORE-MUS-PB|AF-LT-003|CORE-ROM-ANK-INV|CORE-ROM-ANK-EV|CORE-CAP-EV</x:v>
+      </x:c>
+      <x:c r="G48" t="str">
+        <x:v>CORE-ROM-ANK-DF|AF-JNT-002</x:v>
+      </x:c>
+      <x:c r="H48" t="str">
+        <x:v>CORE-MUS-PT|CORE-MUS-EDL|AF-TASK-001|AF-SPT-001|AF-SPT-002|AF-SPT-003|CORE-SPT-NEURO-DISTAL</x:v>
+      </x:c>
+      <x:c r="I48" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J48" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K48" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验踝足主动活动、抗阻及附属活动章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L48" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M48" s="20" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="210" customHeight="1">
+      <x:c r="A49" t="str">
+        <x:v>LOC-AF-R-004</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>跟腱中段与踝后方</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>AF-R-004</x:v>
+      </x:c>
+      <x:c r="D49" t="str">
+        <x:v>ANKLE_FOOT</x:v>
+      </x:c>
+      <x:c r="E49" t="str">
+        <x:v>肌腱与肌群：跟腱中段；腓肠肌与比目鱼肌远端
+周围组织：跟腱周围结缔组织
+神经：后外侧邻近腓肠神经</x:v>
+      </x:c>
+      <x:c r="F49" t="str">
+        <x:v>AF-LT-004|CORE-MUS-GASTROC|CORE-MUS-SOLEUS|CORE-ROM-ANK-DF|CORE-CAP-PF</x:v>
+      </x:c>
+      <x:c r="G49" t="str">
+        <x:v>CORE-MUS-PLANTARIS|CORE-ROM-ANK-EV|CORE-ROM-ANK-PF</x:v>
+      </x:c>
+      <x:c r="H49" t="str">
+        <x:v>CORE-MUS-TP|CORE-MUS-FHL|CORE-MUS-FDL|AF-TASK-002|CORE-SPT-NEURO-DISTAL</x:v>
+      </x:c>
+      <x:c r="I49" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J49" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K49" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验踝足主动活动、抗阻及附属活动章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L49" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M49" s="20" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="210" customHeight="1">
+      <x:c r="A50" t="str">
+        <x:v>LOC-AF-R-005</x:v>
+      </x:c>
+      <x:c r="B50" t="str">
+        <x:v>跟腱止点与跟骨后方</x:v>
+      </x:c>
+      <x:c r="C50" t="str">
+        <x:v>AF-R-005</x:v>
+      </x:c>
+      <x:c r="D50" t="str">
+        <x:v>ANKLE_FOOT</x:v>
+      </x:c>
+      <x:c r="E50" t="str">
+        <x:v>骨与肌腱：跟骨后方；跟腱止点
+周围组织：跟骨后滑囊；跟腱皮下滑囊</x:v>
+      </x:c>
+      <x:c r="F50" t="str">
+        <x:v>AF-LT-005|CORE-MUS-GASTROC|CORE-MUS-SOLEUS|CORE-ROM-ANK-DF|CORE-CAP-PF</x:v>
+      </x:c>
+      <x:c r="G50" t="str">
+        <x:v>CORE-MUS-PLANTARIS|CORE-ROM-ANK-EV|CORE-ROM-ANK-PF</x:v>
+      </x:c>
+      <x:c r="H50" t="str">
+        <x:v>AF-TASK-002|CORE-SPT-NEURO-DISTAL</x:v>
+      </x:c>
+      <x:c r="I50" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J50" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K50" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验踝足主动活动、抗阻及附属活动章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L50" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M50" s="20" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="210" customHeight="1">
+      <x:c r="A51" t="str">
+        <x:v>LOC-AF-HEEL-MEDIAL</x:v>
+      </x:c>
+      <x:c r="B51" t="str">
+        <x:v>足跟底内侧／足底筋膜附着邻近</x:v>
+      </x:c>
+      <x:c r="C51" t="str">
+        <x:v>AF-R-006</x:v>
+      </x:c>
+      <x:c r="D51" t="str">
+        <x:v>ANKLE_FOOT</x:v>
+      </x:c>
+      <x:c r="E51" t="str">
+        <x:v>骨与附着：跟骨内侧结节；足底筋膜近端
+周围组织：足跟脂肪垫；足内在肌邻近</x:v>
+      </x:c>
+      <x:c r="F51" t="str">
+        <x:v>AF-LT-007|AF-LT-006|CORE-ROM-ANK-DF|CORE-MUS-GASTROC|CORE-MUS-SOLEUS|CORE-CAP-ARCH-TOE</x:v>
+      </x:c>
+      <x:c r="G51" t="str">
+        <x:v>CORE-CAP-PF|AF-SPT-004|AF-MUS-016|CORE-ROM-ANK-EV</x:v>
+      </x:c>
+      <x:c r="H51" t="str">
+        <x:v>CORE-ROM-ANK-INV|CORE-SPT-NEURO-DISTAL</x:v>
+      </x:c>
+      <x:c r="I51" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J51" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K51" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验踝足主动活动、抗阻及附属活动章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L51" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M51" s="20" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="210" customHeight="1">
+      <x:c r="A52" t="str">
+        <x:v>LOC-AF-FIRST-MTP-PLANTAR</x:v>
+      </x:c>
+      <x:c r="B52" t="str">
+        <x:v>第一跖趾关节足底侧／籽骨邻近</x:v>
+      </x:c>
+      <x:c r="C52" t="str">
+        <x:v>AF-R-012</x:v>
+      </x:c>
+      <x:c r="D52" t="str">
+        <x:v>ANKLE_FOOT</x:v>
+      </x:c>
+      <x:c r="E52" t="str">
+        <x:v>骨与关节：第一跖骨头；第一跖趾关节；籽骨
+肌肉与肌腱：拇短屈肌；拇长屈肌腱
+周围组织：跖板；关节囊</x:v>
+      </x:c>
+      <x:c r="F52" t="str">
+        <x:v>AF-LT-012|AF-MUS-017|CORE-MUS-FHL|AF-ASM-004|CORE-CAP-HF</x:v>
+      </x:c>
+      <x:c r="G52" t="str">
+        <x:v>AF-MUS-014|AF-MUS-015|AF-JNT-004|CORE-CAP-ARCH-TOE|CORE-MUS-EHL|CORE-MUS-PL|CORE-ROM-ANK-DF|CORE-ROM-ANK-EV</x:v>
+      </x:c>
+      <x:c r="H52" t="str">
+        <x:v>AF-TASK-002|CORE-SPT-NEURO-DISTAL</x:v>
+      </x:c>
+      <x:c r="I52" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J52" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K52" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验踝足主动活动、抗阻及附属活动章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L52" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M52" s="20" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="210" customHeight="1">
+      <x:c r="A53" t="str">
+        <x:v>LOC-THIGH-ANTCENT</x:v>
+      </x:c>
+      <x:c r="B53" t="str">
+        <x:v>大腿前中央／股直肌邻近</x:v>
+      </x:c>
+      <x:c r="C53" t="str">
+        <x:v>THIGH-R-001</x:v>
+      </x:c>
+      <x:c r="D53" t="str">
+        <x:v>THIGH</x:v>
+      </x:c>
+      <x:c r="E53" t="str">
+        <x:v>肌肉：股直肌
+深层邻近：股中间肌
+两侧邻近：股内侧肌；股外侧肌
+远端邻近：股四头肌腱</x:v>
+      </x:c>
+      <x:c r="F53" t="str">
+        <x:v>CORE-MUS-RF|THIGH-LT-001|KNEE-ROM-FLEX|CORE-CAP-KNEE-EXT</x:v>
+      </x:c>
+      <x:c r="G53" t="str">
+        <x:v>CORE-MUS-VI|CORE-MUS-VM|CORE-MUS-VL|KNEE-ROM-EXT|CORE-CAP-QUAD-RECRUIT|CORE-MUS-SART</x:v>
+      </x:c>
+      <x:c r="H53" t="str">
+        <x:v>CORE-SPT-NEURO-DISTAL|THIGH-SPT-NEURO|THIGH-PATTERN-GAIT|THIGH-PATTERN-SAGITTAL|THIGH-PATTERN-LATERAL</x:v>
+      </x:c>
+      <x:c r="I53" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J53" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K53" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验膝部主动活动与抗阻章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L53" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M53" s="20" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="210" customHeight="1">
+      <x:c r="A54" t="str">
+        <x:v>LOC-THIGH-MEDIAL-GRAC</x:v>
+      </x:c>
+      <x:c r="B54" t="str">
+        <x:v>大腿内侧／股薄肌邻近</x:v>
+      </x:c>
+      <x:c r="C54" t="str">
+        <x:v>THIGH-R-003</x:v>
+      </x:c>
+      <x:c r="D54" t="str">
+        <x:v>THIGH</x:v>
+      </x:c>
+      <x:c r="E54" t="str">
+        <x:v>肌肉：股薄肌
+邻近肌群：内收长肌；内收大肌；缝匠肌
+远端附着邻近：鹅足肌腱</x:v>
+      </x:c>
+      <x:c r="F54" t="str">
+        <x:v>CORE-MUS-GRAC|THIGH-LT-003|KNEE-ROM-EXT|KNEE-ROM-FLEX|THIGH-CAP-ADD</x:v>
+      </x:c>
+      <x:c r="G54" t="str">
+        <x:v>CORE-MUS-SART|THIGH-MUS-AL|THIGH-MUS-AM|THIGH-MUS-AB</x:v>
+      </x:c>
+      <x:c r="H54" t="str">
+        <x:v>CORE-SPT-NEURO-DISTAL|THIGH-SPT-NEURO|THIGH-PATTERN-GAIT|THIGH-PATTERN-SAGITTAL|THIGH-PATTERN-LATERAL</x:v>
+      </x:c>
+      <x:c r="I54" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J54" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K54" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验膝部主动活动与抗阻章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L54" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M54" s="20" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="210" customHeight="1">
+      <x:c r="A55" t="str">
+        <x:v>LOC-THIGH-MEDIAL-ADD</x:v>
+      </x:c>
+      <x:c r="B55" t="str">
+        <x:v>大腿内侧／内收肌腹邻近</x:v>
+      </x:c>
+      <x:c r="C55" t="str">
+        <x:v>THIGH-R-003</x:v>
+      </x:c>
+      <x:c r="D55" t="str">
+        <x:v>THIGH</x:v>
+      </x:c>
+      <x:c r="E55" t="str">
+        <x:v>肌肉：内收长肌；内收大肌
+深层邻近：内收短肌；耻骨肌
+浅表邻近：股薄肌；缝匠肌
+骨与周围组织：股骨内侧；内收肌筋膜</x:v>
+      </x:c>
+      <x:c r="F55" t="str">
+        <x:v>THIGH-MUS-AL|THIGH-MUS-AM|THIGH-LT-003|THIGH-CAP-ADD</x:v>
+      </x:c>
+      <x:c r="G55" t="str">
+        <x:v>THIGH-MUS-AB|CORE-MUS-GRAC|CORE-MUS-SART|KNEE-ROM-EXT|KNEE-ROM-FLEX</x:v>
+      </x:c>
+      <x:c r="H55" t="str">
+        <x:v>CORE-SPT-NEURO-DISTAL|THIGH-SPT-NEURO|THIGH-PATTERN-GAIT|THIGH-PATTERN-SAGITTAL|THIGH-PATTERN-LATERAL</x:v>
+      </x:c>
+      <x:c r="I55" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J55" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K55" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验膝部主动活动与抗阻章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L55" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M55" s="20" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="210" customHeight="1">
+      <x:c r="A56" t="str">
+        <x:v>LOC-LL-GASTROC-MEDIAL</x:v>
+      </x:c>
+      <x:c r="B56" t="str">
+        <x:v>小腿后侧／腓肠肌内侧头邻近</x:v>
+      </x:c>
+      <x:c r="C56" t="str">
+        <x:v>LL-R-005</x:v>
+      </x:c>
+      <x:c r="D56" t="str">
+        <x:v>LOWER_LEG</x:v>
+      </x:c>
+      <x:c r="E56" t="str">
+        <x:v>表浅肌群：腓肠肌内侧头
+深层邻近：比目鱼肌
+近端邻近：膝后内侧肌腱；膝后关节囊
+远端邻近：腓肠肌腱膜；跟腱</x:v>
+      </x:c>
+      <x:c r="F56" t="str">
+        <x:v>CORE-MUS-GASTROC|LL-LT-005|CORE-ROM-ANK-DF|CORE-CAP-PF</x:v>
+      </x:c>
+      <x:c r="G56" t="str">
+        <x:v>CORE-MUS-SOLEUS|CORE-MUS-TP|CORE-MUS-FDL|CORE-MUS-PLANTARIS</x:v>
+      </x:c>
+      <x:c r="H56" t="str">
+        <x:v>LL-SPT-001|CORE-SPT-NEURO-DISTAL|LL-PATTERN-GAIT|LL-PATTERN-PUSH|LL-PATTERN-IMPACT</x:v>
+      </x:c>
+      <x:c r="I56" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J56" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K56" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验膝部主动活动与抗阻章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L56" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M56" s="20" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="210" customHeight="1">
+      <x:c r="A57" t="str">
+        <x:v>LOC-LL-GASTROC-LATERAL</x:v>
+      </x:c>
+      <x:c r="B57" t="str">
+        <x:v>小腿后侧／腓肠肌外侧头邻近</x:v>
+      </x:c>
+      <x:c r="C57" t="str">
+        <x:v>LL-R-005</x:v>
+      </x:c>
+      <x:c r="D57" t="str">
+        <x:v>LOWER_LEG</x:v>
+      </x:c>
+      <x:c r="E57" t="str">
+        <x:v>表浅肌群：腓肠肌外侧头
+深层邻近：比目鱼肌
+近端邻近：股二头肌腱；腓骨头
+远端邻近：腓肠肌腱膜；跟腱</x:v>
+      </x:c>
+      <x:c r="F57" t="str">
+        <x:v>CORE-MUS-GASTROC|LL-LT-005|CORE-ROM-ANK-DF|CORE-CAP-PF</x:v>
+      </x:c>
+      <x:c r="G57" t="str">
+        <x:v>CORE-MUS-SOLEUS|CORE-MUS-PL|CORE-MUS-PB|CORE-MUS-PLANTARIS</x:v>
+      </x:c>
+      <x:c r="H57" t="str">
+        <x:v>LL-SPT-001|CORE-SPT-NEURO-DISTAL|LL-PATTERN-GAIT|LL-PATTERN-PUSH|LL-PATTERN-IMPACT</x:v>
+      </x:c>
+      <x:c r="I57" t="str">
+        <x:v>MUSCLE_STATE:邻近肌群|ROM:相关关节活动|CAPACITY:相关肌力|LOCAL:局部组织|SPECIAL_TEST:补充检查|FUNCTION:相关动作观察</x:v>
+      </x:c>
+      <x:c r="J57" t="str">
+        <x:v>待临床审核</x:v>
+      </x:c>
+      <x:c r="K57" t="str">
+        <x:v>BodyParts3D 4.0 原始模型具名组织及骨性标志；既有01_Region、02_ClinicalItem及评估/处理关联；book://magee-local，已核验膝部主动活动与抗阻章节（见reference_books_verified_v1.json）。本次只调整阅读入口和组织关联，不新增治疗方法。</x:v>
+      </x:c>
+      <x:c r="L57" t="str">
+        <x:v>区域是周围组织与评估参考的阅读入口。主要项目直接展示，补充项目按需展开。沿用既有检查与处理内容，不以模型选点确定疼痛组织。</x:v>
+      </x:c>
+      <x:c r="M57" s="20" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
